--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Roles" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$S$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$T$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D71"/>
+  <dimension ref="B2:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>How much this change will be felt by clinicians. High means the design conversation matters more than the technology.</t>
+          <t>Stable = record it once and it holds. Drifts = it goes stale unless somebody keeps asking, so it needs a standing engagement mechanism, not a field captured at start of care. Live/computed = recalculated, no decay problem. This is the contact = the row is the outbound work itself.</t>
         </is>
       </c>
     </row>
@@ -1193,294 +1193,326 @@
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>High adoption sensitivity</t>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Rows where the change lands on clinicians. Design these with them.</t>
+          <t>THE ENGAGEMENT LOAD. These go stale unless somebody keeps asking.</t>
         </is>
       </c>
       <c r="D43" s="12">
-        <f>COUNTIF('Master List'!$Q$2:$Q$89,"High")</f>
+        <f>COUNTIF('Master List'!$O$2:$O$89,"Drifts*")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Day-one must-haves</t>
+          <t>...and sitting outside Engagement</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MVP = Yes.</t>
+          <t>Capacity and scheduling rows that still need an engagement mechanism under them.</t>
         </is>
       </c>
       <c r="D44" s="12">
-        <f>COUNTIF('Master List'!$O$2:$O$89,"Yes")</f>
+        <f>COUNTIFS('Master List'!$O$2:$O$89,"Drifts*",'Master List'!$B$2:$B$89,"&lt;&gt;Patient Engagement")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
+          <t>High adoption sensitivity</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Rows where the change lands on clinicians. Design these with them.</t>
+        </is>
+      </c>
+      <c r="D45" s="12">
+        <f>COUNTIF('Master List'!$R$2:$R$89,"High")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Day-one must-haves</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>MVP = Yes.</t>
+        </is>
+      </c>
+      <c r="D46" s="12">
+        <f>COUNTIF('Master List'!$P$2:$P$89,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
           <t>Knockout requirements</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Gating = Y. A product that cannot do these should not advance.</t>
         </is>
       </c>
-      <c r="D45" s="12">
-        <f>COUNTIF('Master List'!$P$2:$P$89,"Y")</f>
+      <c r="D47" s="12">
+        <f>COUNTIF('Master List'!$Q$2:$Q$89,"Y")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>A worked row, so the expected format is obvious</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Arena (8.19 workbook)</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>Capacity Management</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Also touches</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>C-03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>One-pager group</t>
+          <t>Arena (8.19 workbook)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>Availability &amp; reach</t>
+          <t>Capacity Management</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Placement check</t>
+          <t>Also touches</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>Aligned</t>
+          <t>Scheduling</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>In plain terms</t>
+          <t>One-pager group</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>Which zip codes each clinician covers. Territories were drawn on thin data and have stayed static, so capacity drifts away from demand quietly.</t>
+          <t>Availability &amp; reach</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Who does the work today</t>
+          <t>Placement check</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>DCS and Scheduler — assign and adjust</t>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Who reads it and decides today</t>
+          <t>In plain terms</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Branch Leadership (ED) with DCS — at the joint review when capacity tightens</t>
+          <t>Which zip codes each clinician covers. Territories were drawn on thin data and have stayed static, so capacity drifts away from demand quietly.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Where it lives today</t>
+          <t>Who does the work today</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>HCHB holds the assignment where it has been entered; the working version is often the scheduler's own reference.</t>
+          <t>DCS and Scheduler — assign and adjust</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Who reads it and decides today</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Branch Leadership (ED) with DCS — at the joint review when capacity tightens</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Future state</t>
+          <t>Where it lives today</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>Assist — the tool proposes territory changes against a live census heat-map</t>
+          <t>HCHB holds the assignment where it has been entered; the working version is often the scheduler's own reference.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Future state -- who decides</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>Branch Leadership (ED) with DCS</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Trigger / how often</t>
+          <t>Future state</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>Quarterly, or on demand shift</t>
+          <t>Assist — the tool proposes territory changes against a live census heat-map</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Future state -- who decides</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Branch Leadership (ED) with DCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Trigger / how often</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Quarterly, or on demand shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Adoption sensitivity</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="3" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Editing conventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Everything is editable</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Nothing is locked. The drop-down columns accept typed values too, so a shared answer like 'DCS and Scheduler' is always allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Say 'no one' when it is true</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>If nobody reads a report today, write '— no one today'. Those rows are counted above and they are where the value is.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Keep IDs untouched</t>
+          <t>Everything is editable</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>The ID column is the join key back to the 8.13 workbook. Never renumber it.</t>
+          <t>Nothing is locked. The drop-down columns accept typed values too, so a shared answer like 'DCS and Scheduler' is always allowed.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
+          <t>Say 'no one' when it is true</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>If nobody reads a report today, write '— no one today'. Those rows are counted above and they are where the value is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Keep IDs untouched</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>The ID column is the join key back to the 8.13 workbook. Never renumber it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
           <t>This does not overwrite the workbook</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>The 8.13 workbook stays authoritative for the variables themselves. This sheet adds the ownership and future-state layer on top.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="14" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>Sources: variables and IDs from the 8.13 Compassus Capacity &amp; Scheduling Workbook (Variable Inventory + Definitions &amp; Concepts tabs). Plain-language wording follows the vendor one-pager as it stands in the 21 Aug questionnaire Overview tab. Current-state ownership follows the 17-18 Aug flow-mapping facts. Where-it-lives entries are first-pass hypotheses, not findings -- the confidence shading says how much to trust each one.</t>
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B71:C73"/>
     <mergeCell ref="B3:C4"/>
-    <mergeCell ref="B69:C71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1492,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:T89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1509,11 +1541,12 @@
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="62" customWidth="1" min="18" max="18"/>
-    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="62" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1589,25 +1622,30 @@
       </c>
       <c r="O1" s="15" t="inlineStr">
         <is>
+          <t>Stays true on its own?</t>
+        </is>
+      </c>
+      <c r="P1" s="15" t="inlineStr">
+        <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="P1" s="15" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Gating</t>
         </is>
       </c>
-      <c r="Q1" s="15" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>Adoption sensitivity</t>
         </is>
       </c>
-      <c r="R1" s="15" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>Why this posture / watch-out</t>
         </is>
       </c>
-      <c r="S1" s="15" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>Open question for the team</t>
         </is>
@@ -1684,27 +1722,32 @@
           <t>Continuous — changes on hire/term</t>
         </is>
       </c>
-      <c r="O2" s="22" t="inlineStr">
+      <c r="O2" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P2" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P2" s="22" t="inlineStr">
+      <c r="Q2" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q2" s="21" t="inlineStr">
+      <c r="R2" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R2" s="18" t="inlineStr">
+      <c r="S2" s="18" t="inlineStr">
         <is>
           <t>A clean roster fact in a system of record. The only risk is Workday and HCHB disagreeing.</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="T2" s="18" t="inlineStr">
         <is>
           <t>Which system wins when Workday and HCHB disagree on who is active?</t>
         </is>
@@ -1781,27 +1824,32 @@
           <t>Continuous — changes on hire/term</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q3" s="21" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R3" s="18" t="inlineStr">
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t>Hard licensure fact, fully in the data.</t>
         </is>
       </c>
-      <c r="S3" s="18" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
         <is>
           <t>Are the discipline codes identical in Workday and HCHB, or do they need mapping?</t>
         </is>
@@ -1878,27 +1926,32 @@
           <t>Continuous — derived</t>
         </is>
       </c>
-      <c r="O4" s="22" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P4" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R4" s="18" t="inlineStr">
+      <c r="S4" s="18" t="inlineStr">
         <is>
           <t>Deterministic from discipline. The sensitivity is not the data, it is the change-management of moving work to assistants.</t>
         </is>
       </c>
-      <c r="S4" s="18" t="inlineStr">
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t>Is the assessing/assistant split written down as policy anywhere, or only understood?</t>
         </is>
@@ -1971,27 +2024,32 @@
           <t>Continuous — changes on status change</t>
         </is>
       </c>
-      <c r="O5" s="22" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R5" s="18" t="inlineStr">
+      <c r="S5" s="18" t="inlineStr">
         <is>
           <t>Clean employment attribute. Flagged as a conflict risk: a vendor that models FTE differently will fight the branch.</t>
         </is>
       </c>
-      <c r="S5" s="18" t="inlineStr">
+      <c r="T5" s="18" t="inlineStr">
         <is>
           <t>Do per-diem and contract clinicians carry an FTE value at all, or are they null?</t>
         </is>
@@ -2064,27 +2122,32 @@
           <t>Continuous</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R6" s="18" t="inlineStr">
+      <c r="S6" s="18" t="inlineStr">
         <is>
           <t>A branch is only as capable as its thinnest discipline; this is the view that shows it.</t>
         </is>
       </c>
-      <c r="S6" s="18" t="inlineStr">
+      <c r="T6" s="18" t="inlineStr">
         <is>
           <t>Who owns the branch roll-up today — is anyone producing this view at all?</t>
         </is>
@@ -2161,27 +2224,32 @@
           <t>On event — call-outs and admission spikes</t>
         </is>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="S7" s="18" t="inlineStr">
         <is>
           <t>The size of the buffer is legible; whether it actually flexes is relational. The system can show who is available, never assume they will say yes.</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr">
+      <c r="T7" s="18" t="inlineStr">
         <is>
           <t>Is there a maintained per-diem availability list anywhere, or is it rebuilt from memory each time?</t>
         </is>
@@ -2258,27 +2326,32 @@
           <t>Slow-changing — on certification or experience</t>
         </is>
       </c>
-      <c r="O8" s="22" t="inlineStr">
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="inlineStr">
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R8" s="18" t="inlineStr">
+      <c r="S8" s="18" t="inlineStr">
         <is>
           <t>Competency lives partly in reputation, not credentials. Surfacing it is useful; scoring it is not.</t>
         </is>
       </c>
-      <c r="S8" s="18" t="inlineStr">
+      <c r="T8" s="18" t="inlineStr">
         <is>
           <t>Is there a competency list per clinician anywhere today, and who would own keeping it current?</t>
         </is>
@@ -2351,27 +2424,32 @@
           <t>Weekly during onboarding</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P9" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R9" s="18" t="inlineStr">
+      <c r="S9" s="18" t="inlineStr">
         <is>
           <t>Headcount is clear; the true ramp curve is judgment. A system can propose a curve, a manager corrects it.</t>
         </is>
       </c>
-      <c r="S9" s="18" t="inlineStr">
+      <c r="T9" s="18" t="inlineStr">
         <is>
           <t>Is there a standard ramp expectation by discipline, or is it manager-by-manager?</t>
         </is>
@@ -2448,27 +2526,32 @@
           <t>Weekly</t>
         </is>
       </c>
-      <c r="O10" s="22" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P10" s="22" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q10" s="21" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="S10" s="18" t="inlineStr">
         <is>
           <t>Legible load once the rotation is recorded. The fairness question is human.</t>
         </is>
       </c>
-      <c r="S10" s="18" t="inlineStr">
+      <c r="T10" s="18" t="inlineStr">
         <is>
           <t>Is the rotation kept in HCHB, or on a separate branch calendar?</t>
         </is>
@@ -2545,27 +2628,32 @@
           <t>On event — coverage and surge</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="Q11" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R11" s="18" t="inlineStr">
+      <c r="S11" s="18" t="inlineStr">
         <is>
           <t>A purely relational variable: the act of automating it changes what it measures. Surface who has said yes before; never auto-assign on it.</t>
         </is>
       </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="T11" s="18" t="inlineStr">
         <is>
           <t>Would clinicians accept this being visible at all? This is a trust question before it is a data question.</t>
         </is>
@@ -2642,27 +2730,32 @@
           <t>On event — coverage and surge</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P12" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P12" s="22" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R12" s="18" t="inlineStr">
+      <c r="S12" s="18" t="inlineStr">
         <is>
           <t>Relational and pay-linked. This is the row that connects to the incentives idea in the one-pager: today there is no mechanism, only a phone call.</t>
         </is>
       </c>
-      <c r="S12" s="18" t="inlineStr">
+      <c r="T12" s="18" t="inlineStr">
         <is>
           <t>If we attach an incentive to hard-to-fill visits, who sets it and who approves the spend?</t>
         </is>
@@ -2739,27 +2832,32 @@
           <t>Continuous — as requests are approved</t>
         </is>
       </c>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q13" s="21" t="inlineStr">
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R13" s="18" t="inlineStr">
+      <c r="S13" s="18" t="inlineStr">
         <is>
           <t>A firm blackout once it is in the field. The integration being off is the single highest-value plumbing fix on this sheet — it makes every capacity number stale.</t>
         </is>
       </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="T13" s="18" t="inlineStr">
         <is>
           <t>What would it take to turn the Workday-to-HCHB availability integration back on?</t>
         </is>
@@ -2836,27 +2934,32 @@
           <t>Quarterly, or when capacity tightens</t>
         </is>
       </c>
-      <c r="O14" s="22" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P14" s="22" t="inlineStr">
+      <c r="Q14" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="S14" s="18" t="inlineStr">
         <is>
           <t>Territory lines look fixed but encode local knowledge and standing agreements. A tool should propose changes, never redraw them.</t>
         </is>
       </c>
-      <c r="S14" s="18" t="inlineStr">
+      <c r="T14" s="18" t="inlineStr">
         <is>
           <t>Is the current zip-to-clinician assignment complete in HCHB, or does the scheduler hold part of it?</t>
         </is>
@@ -2929,27 +3032,32 @@
           <t>Config — set once, revisited rarely</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="R15" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R15" s="18" t="inlineStr">
+      <c r="S15" s="18" t="inlineStr">
         <is>
           <t>Fixed boundary, cleanly held in configuration.</t>
         </is>
       </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="T15" s="18" t="inlineStr">
         <is>
           <t>Does the recorded coverage area match what the branch actually accepts in practice?</t>
         </is>
@@ -3026,27 +3134,32 @@
           <t>Quarterly, or on demand shift</t>
         </is>
       </c>
-      <c r="O16" s="22" t="inlineStr">
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P16" s="22" t="inlineStr">
+      <c r="Q16" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q16" s="21" t="inlineStr">
+      <c r="R16" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R16" s="18" t="inlineStr">
+      <c r="S16" s="18" t="inlineStr">
         <is>
           <t>Called out in the inventory as the initial variable in the whole equation. Pairing it with a live census heat-map is the highest-leverage capacity change identified.</t>
         </is>
       </c>
-      <c r="S16" s="18" t="inlineStr">
+      <c r="T16" s="18" t="inlineStr">
         <is>
           <t>How current is the zip assignment in HCHB right now — and when was it last reviewed against referral patterns?</t>
         </is>
@@ -3119,27 +3232,32 @@
           <t>One-time decision</t>
         </is>
       </c>
-      <c r="O17" s="22" t="inlineStr">
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P17" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R17" s="18" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t>A modelling choice, not a live control. It reshapes both the capacity map and the routing at once, so it should be decided on purpose rather than inherited from a vendor default.</t>
         </is>
       </c>
-      <c r="S17" s="18" t="inlineStr">
+      <c r="T17" s="18" t="inlineStr">
         <is>
           <t>Do we want to make this call before vendor selection, or let the shortlist show us what is practical?</t>
         </is>
@@ -3216,27 +3334,32 @@
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="O18" s="22" t="inlineStr">
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q18" s="21" t="inlineStr">
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R18" s="18" t="inlineStr">
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. The workbook's own example is the whole argument: one territory carrying about thirty patients across two full-time clinicians while the adjacent area declines starts. The tool proposes the misalignment; a person moves the boundary.</t>
         </is>
       </c>
-      <c r="S18" s="18" t="inlineStr">
+      <c r="T18" s="18" t="inlineStr">
         <is>
           <t>What cadence do we want for territory review, and who convenes it?</t>
         </is>
@@ -3313,27 +3436,32 @@
           <t>Weekly</t>
         </is>
       </c>
-      <c r="O19" s="22" t="inlineStr">
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="Q19" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q19" s="21" t="inlineStr">
+      <c r="R19" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R19" s="18" t="inlineStr">
+      <c r="S19" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and deliberately read-only. Inferring the preference from observed start times would record defeat as choice and then optimise to preserve it. Ask, record the answer, report the gap.</t>
         </is>
       </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="T19" s="18" t="inlineStr">
         <is>
           <t>Who asks, and how often? This only works if the answer is collected rather than derived.</t>
         </is>
@@ -3410,27 +3538,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O20" s="22" t="inlineStr">
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P20" s="22" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q20" s="21" t="inlineStr">
+      <c r="R20" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R20" s="18" t="inlineStr">
+      <c r="S20" s="18" t="inlineStr">
         <is>
           <t>Derived and safe to compute. The catch is pending-auth visits, which are on no calendar and count toward nothing — so this number is already understated today.</t>
         </is>
       </c>
-      <c r="S20" s="18" t="inlineStr">
+      <c r="T20" s="18" t="inlineStr">
         <is>
           <t>Confirm which HCHB view the branch actually uses for committed points, and whether pending-auth visits appear anywhere in it.</t>
         </is>
@@ -3507,27 +3640,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O21" s="22" t="inlineStr">
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P21" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P21" s="22" t="inlineStr">
+      <c r="Q21" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="R21" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R21" s="18" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>Pure derivation, but only as good as the point definitions underneath it. This is one of the clearest 'nobody can see this today' rows.</t>
         </is>
       </c>
-      <c r="S21" s="18" t="inlineStr">
+      <c r="T21" s="18" t="inlineStr">
         <is>
           <t>Does any current HCHB view show open points by day, or is this genuinely net-new?</t>
         </is>
@@ -3600,27 +3738,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O22" s="22" t="inlineStr">
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P22" s="22" t="inlineStr">
+      <c r="Q22" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q22" s="21" t="inlineStr">
+      <c r="R22" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R22" s="18" t="inlineStr">
+      <c r="S22" s="18" t="inlineStr">
         <is>
           <t>The headline capacity number. Everything else on this sheet exists to make it trustworthy.</t>
         </is>
       </c>
-      <c r="S22" s="18" t="inlineStr">
+      <c r="T22" s="18" t="inlineStr">
         <is>
           <t>What is the decision this number should drive, and who makes it — ED, DCS, or intake?</t>
         </is>
@@ -3697,27 +3840,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O23" s="22" t="inlineStr">
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="R23" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R23" s="18" t="inlineStr">
+      <c r="S23" s="18" t="inlineStr">
         <is>
           <t>The growth-gating number. Distinct from total open room and more binding.</t>
         </is>
       </c>
-      <c r="S23" s="18" t="inlineStr">
+      <c r="T23" s="18" t="inlineStr">
         <is>
           <t>How does the branch decide today whether it can take another admission — what is the current proxy?</t>
         </is>
@@ -3794,27 +3942,32 @@
           <t>Config — set once, revisited by policy</t>
         </is>
       </c>
-      <c r="O24" s="22" t="inlineStr">
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P24" s="22" t="inlineStr">
+      <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="inlineStr">
+      <c r="R24" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R24" s="18" t="inlineStr">
+      <c r="S24" s="18" t="inlineStr">
         <is>
           <t>The values exist. What is undefined is how travel, documentation time and acuity are treated — and until that is settled, every derived capacity number inherits the ambiguity.</t>
         </is>
       </c>
-      <c r="S24" s="18" t="inlineStr">
+      <c r="T24" s="18" t="inlineStr">
         <is>
           <t>Open question #1: do points account for travel, documentation and acuity, or only visit type?</t>
         </is>
@@ -3887,27 +4040,32 @@
           <t>Config</t>
         </is>
       </c>
-      <c r="O25" s="22" t="inlineStr">
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P25" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P25" s="22" t="inlineStr">
+      <c r="Q25" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q25" s="21" t="inlineStr">
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R25" s="18" t="inlineStr">
+      <c r="S25" s="18" t="inlineStr">
         <is>
           <t>A policy constant and a simple lookup. Conflict risk: a vendor with its own opinion about targets will fight branch policy.</t>
         </is>
       </c>
-      <c r="S25" s="18" t="inlineStr">
+      <c r="T25" s="18" t="inlineStr">
         <is>
           <t>Are targets uniform across branches and disciplines, or do they vary?</t>
         </is>
@@ -3984,27 +4142,32 @@
           <t>Continuous — as events occur</t>
         </is>
       </c>
-      <c r="O26" s="22" t="inlineStr">
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P26" s="22" t="inlineStr">
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q26" s="21" t="inlineStr">
+      <c r="R26" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R26" s="18" t="inlineStr">
+      <c r="S26" s="18" t="inlineStr">
         <is>
           <t>Detecting the events is straightforward. What to do about the trend is the judgment, and it sits with the branch.</t>
         </is>
       </c>
-      <c r="S26" s="18" t="inlineStr">
+      <c r="T26" s="18" t="inlineStr">
         <is>
           <t>Is discharge date reliable enough in HCHB to forecast returning capacity?</t>
         </is>
@@ -4077,27 +4240,32 @@
           <t>Continuous</t>
         </is>
       </c>
-      <c r="O27" s="22" t="inlineStr">
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P27" s="22" t="inlineStr">
+      <c r="Q27" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q27" s="21" t="inlineStr">
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R27" s="18" t="inlineStr">
+      <c r="S27" s="18" t="inlineStr">
         <is>
           <t>Out of scope by choice, documented so the capacity math is transparent about what it holds constant.</t>
         </is>
       </c>
-      <c r="S27" s="18" t="inlineStr">
+      <c r="T27" s="18" t="inlineStr">
         <is>
           <t>Confirm this stays out of scope as the initiative moves into future-state design.</t>
         </is>
@@ -4174,27 +4342,32 @@
           <t>Slow-changing, with informal exceptions</t>
         </is>
       </c>
-      <c r="O28" s="22" t="inlineStr">
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q28" s="21" t="inlineStr">
+      <c r="R28" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R28" s="18" t="inlineStr">
+      <c r="S28" s="18" t="inlineStr">
         <is>
           <t>A set pattern with informal exceptions — the exceptions are the part no system holds.</t>
         </is>
       </c>
-      <c r="S28" s="18" t="inlineStr">
+      <c r="T28" s="18" t="inlineStr">
         <is>
           <t>Are working patterns recorded in HCHB per clinician, or reconstructed by the scheduler each week?</t>
         </is>
@@ -4267,27 +4440,32 @@
           <t>Daily, in practice</t>
         </is>
       </c>
-      <c r="O29" s="22" t="inlineStr">
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P29" s="22" t="inlineStr">
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="inlineStr">
+      <c r="R29" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R29" s="18" t="inlineStr">
+      <c r="S29" s="18" t="inlineStr">
         <is>
           <t>Preferred and possible are two different things. Many clinicians want an early first visit and struggle to make it happen; it takes planning and patient motivation, not just a preference field.</t>
         </is>
       </c>
-      <c r="S29" s="18" t="inlineStr">
+      <c r="T29" s="18" t="inlineStr">
         <is>
           <t>Do we want to set a branch expectation on first-visit time, or keep it individual?</t>
         </is>
@@ -4360,27 +4538,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O30" s="22" t="inlineStr">
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P30" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P30" s="22" t="inlineStr">
+      <c r="Q30" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q30" s="21" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R30" s="18" t="inlineStr">
+      <c r="S30" s="18" t="inlineStr">
         <is>
           <t>Depends on a person's willingness. Assuming it is available damages the trust the whole thing runs on — surface only.</t>
         </is>
       </c>
-      <c r="S30" s="18" t="inlineStr">
+      <c r="T30" s="18" t="inlineStr">
         <is>
           <t>None — this row is intentionally read-only.</t>
         </is>
@@ -4453,27 +4636,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O31" s="22" t="inlineStr">
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P31" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P31" s="22" t="inlineStr">
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q31" s="21" t="inlineStr">
+      <c r="R31" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R31" s="18" t="inlineStr">
+      <c r="S31" s="18" t="inlineStr">
         <is>
           <t>A capturable personal habit. Worth knowing, not worth enforcing.</t>
         </is>
       </c>
-      <c r="S31" s="18" t="inlineStr">
+      <c r="T31" s="18" t="inlineStr">
         <is>
           <t>Would clinicians be willing to record this, or does it feel like surveillance?</t>
         </is>
@@ -4546,27 +4734,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O32" s="22" t="inlineStr">
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P32" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P32" s="22" t="inlineStr">
+      <c r="Q32" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q32" s="21" t="inlineStr">
+      <c r="R32" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R32" s="18" t="inlineStr">
+      <c r="S32" s="18" t="inlineStr">
         <is>
           <t>Same shape as the lunch pattern. Note that documentation time is real capacity consumed, and today it is invisible in the point math.</t>
         </is>
       </c>
-      <c r="S32" s="18" t="inlineStr">
+      <c r="T32" s="18" t="inlineStr">
         <is>
           <t>Should documentation time be represented in the point system? Ties to open question #1.</t>
         </is>
@@ -4639,27 +4832,32 @@
           <t>Daily, and it varies</t>
         </is>
       </c>
-      <c r="O33" s="22" t="inlineStr">
+      <c r="O33" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P33" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P33" s="22" t="inlineStr">
+      <c r="Q33" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q33" s="21" t="inlineStr">
+      <c r="R33" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R33" s="18" t="inlineStr">
+      <c r="S33" s="18" t="inlineStr">
         <is>
           <t>A personal daily rhythm that varies. Hard to predict reliably and easily disrupted by a system that assumes it knows — read only.</t>
         </is>
       </c>
-      <c r="S33" s="18" t="inlineStr">
+      <c r="T33" s="18" t="inlineStr">
         <is>
           <t>None — intentionally read-only.</t>
         </is>
@@ -4732,27 +4930,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O34" s="22" t="inlineStr">
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P34" s="22" t="inlineStr">
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q34" s="21" t="inlineStr">
+      <c r="R34" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R34" s="18" t="inlineStr">
+      <c r="S34" s="18" t="inlineStr">
         <is>
           <t>A firm edge once known. The knowing is the tacit part.</t>
         </is>
       </c>
-      <c r="S34" s="18" t="inlineStr">
+      <c r="T34" s="18" t="inlineStr">
         <is>
           <t>Is there a place a clinician could record a standing hard stop today?</t>
         </is>
@@ -4825,27 +5028,32 @@
           <t>Slow-changing</t>
         </is>
       </c>
-      <c r="O35" s="22" t="inlineStr">
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P35" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P35" s="22" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q35" s="21" t="inlineStr">
+      <c r="R35" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R35" s="18" t="inlineStr">
+      <c r="S35" s="18" t="inlineStr">
         <is>
           <t>A personal ceiling, capturable and worth confirming. Conflict risk: a vendor that packs to points alone will breach it.</t>
         </is>
       </c>
-      <c r="S35" s="18" t="inlineStr">
+      <c r="T35" s="18" t="inlineStr">
         <is>
           <t>Do we want a branch-level maximum as well as an individual one?</t>
         </is>
@@ -4922,27 +5130,32 @@
           <t>Slow-changing</t>
         </is>
       </c>
-      <c r="O36" s="22" t="inlineStr">
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P36" s="22" t="inlineStr">
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q36" s="21" t="inlineStr">
+      <c r="R36" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R36" s="18" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>A legible anchor once captured. Using home addresses for routing has a privacy dimension worth settling early.</t>
         </is>
       </c>
-      <c r="S36" s="18" t="inlineStr">
+      <c r="T36" s="18" t="inlineStr">
         <is>
           <t>Can we use clinician home addresses for drive-time calculation, and has that been agreed with them?</t>
         </is>
@@ -5015,27 +5228,32 @@
           <t>Per episode, at plan of care and at each recertification</t>
         </is>
       </c>
-      <c r="O37" s="22" t="inlineStr">
+      <c r="O37" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P37" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P37" s="22" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q37" s="21" t="inlineStr">
+      <c r="R37" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R37" s="18" t="inlineStr">
+      <c r="S37" s="18" t="inlineStr">
         <is>
           <t>Clear in HCHB. Note that each discipline plots to clinical need without seeing payer limits at that moment — which is where the auth collision starts.</t>
         </is>
       </c>
-      <c r="S37" s="18" t="inlineStr">
+      <c r="T37" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding — this row is solid.</t>
         </is>
@@ -5108,27 +5326,32 @@
           <t>Per visit</t>
         </is>
       </c>
-      <c r="O38" s="22" t="inlineStr">
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P38" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P38" s="22" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q38" s="21" t="inlineStr">
+      <c r="R38" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R38" s="18" t="inlineStr">
+      <c r="S38" s="18" t="inlineStr">
         <is>
           <t>Clean order attribute.</t>
         </is>
       </c>
-      <c r="S38" s="18" t="inlineStr">
+      <c r="T38" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5205,27 +5428,32 @@
           <t>Per episode and per add-on order</t>
         </is>
       </c>
-      <c r="O39" s="22" t="inlineStr">
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P39" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P39" s="22" t="inlineStr">
+      <c r="Q39" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q39" s="21" t="inlineStr">
+      <c r="R39" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R39" s="18" t="inlineStr">
+      <c r="S39" s="18" t="inlineStr">
         <is>
           <t>The largest single bottleneck in current-state scheduling, and the most tractable: the rules already exist in writing before they are needed. Surfacing the coordination note at plan-of-care creation is the highest-value, lowest-complexity win identified. Pending-auth visits sit on no calendar and count toward nothing — if you cannot see it, you cannot plan it.</t>
         </is>
       </c>
-      <c r="S39" s="18" t="inlineStr">
+      <c r="T39" s="18" t="inlineStr">
         <is>
           <t>Can the auth coordination note be surfaced into the plan-of-care screen, and who owns that change?</t>
         </is>
@@ -5302,27 +5530,32 @@
           <t>On event — mid-episode</t>
         </is>
       </c>
-      <c r="O40" s="22" t="inlineStr">
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P40" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P40" s="22" t="inlineStr">
+      <c r="Q40" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q40" s="21" t="inlineStr">
+      <c r="R40" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R40" s="18" t="inlineStr">
+      <c r="S40" s="18" t="inlineStr">
         <is>
           <t>Flagged in the inventory as a bottleneck awaiting DCS workflow. It affects how capacity looks as well as what gets scheduled.</t>
         </is>
       </c>
-      <c r="S40" s="18" t="inlineStr">
+      <c r="T40" s="18" t="inlineStr">
         <is>
           <t>What is the current DCS add-on workflow, and is it consistent across branches?</t>
         </is>
@@ -5395,27 +5628,32 @@
           <t>Per visit</t>
         </is>
       </c>
-      <c r="O41" s="22" t="inlineStr">
+      <c r="O41" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P41" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P41" s="22" t="inlineStr">
+      <c r="Q41" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q41" s="21" t="inlineStr">
+      <c r="R41" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R41" s="18" t="inlineStr">
+      <c r="S41" s="18" t="inlineStr">
         <is>
           <t>A hard, legible clock — among the safest things to enforce automatically.</t>
         </is>
       </c>
-      <c r="S41" s="18" t="inlineStr">
+      <c r="T41" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5492,27 +5730,32 @@
           <t>Per referral</t>
         </is>
       </c>
-      <c r="O42" s="22" t="inlineStr">
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P42" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P42" s="22" t="inlineStr">
+      <c r="Q42" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q42" s="21" t="inlineStr">
+      <c r="R42" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R42" s="18" t="inlineStr">
+      <c r="S42" s="18" t="inlineStr">
         <is>
           <t>A hard regulatory clock, fully clear — described in the inventory as the safest automation win available.</t>
         </is>
       </c>
-      <c r="S42" s="18" t="inlineStr">
+      <c r="T42" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5585,27 +5828,32 @@
           <t>Per episode</t>
         </is>
       </c>
-      <c r="O43" s="22" t="inlineStr">
+      <c r="O43" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P43" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P43" s="22" t="inlineStr">
+      <c r="Q43" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q43" s="21" t="inlineStr">
+      <c r="R43" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R43" s="18" t="inlineStr">
+      <c r="S43" s="18" t="inlineStr">
         <is>
           <t>Regulatory window; enforce and flag. Recert visits are already on the calendar from the original plan of care.</t>
         </is>
       </c>
-      <c r="S43" s="18" t="inlineStr">
+      <c r="T43" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5682,27 +5930,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O44" s="22" t="inlineStr">
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P44" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P44" s="22" t="inlineStr">
+      <c r="Q44" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q44" s="21" t="inlineStr">
+      <c r="R44" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R44" s="18" t="inlineStr">
+      <c r="S44" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. Queue depth and age are countable, but the queue is other people's work — surface it in front of the people it blocks, do not reorder it.</t>
         </is>
       </c>
-      <c r="S44" s="18" t="inlineStr">
+      <c r="T44" s="18" t="inlineStr">
         <is>
           <t>Can queue age be reported daily, and who owns acting on it?</t>
         </is>
@@ -5775,27 +6028,32 @@
           <t>Per visit</t>
         </is>
       </c>
-      <c r="O45" s="22" t="inlineStr">
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P45" s="22" t="inlineStr">
+      <c r="Q45" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q45" s="21" t="inlineStr">
+      <c r="R45" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R45" s="18" t="inlineStr">
+      <c r="S45" s="18" t="inlineStr">
         <is>
           <t>A hard gate and fully legible. The sensitivity is the flip side: auto-assigning routine visits to assistants opens a lot of capacity but is a significant change-management conversation.</t>
         </is>
       </c>
-      <c r="S45" s="18" t="inlineStr">
+      <c r="T45" s="18" t="inlineStr">
         <is>
           <t>How far do we want to push routine visits to assistants, and who owns that decision?</t>
         </is>
@@ -5872,27 +6130,32 @@
           <t>Per visit</t>
         </is>
       </c>
-      <c r="O46" s="22" t="inlineStr">
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P46" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P46" s="22" t="inlineStr">
+      <c r="Q46" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q46" s="21" t="inlineStr">
+      <c r="R46" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R46" s="18" t="inlineStr">
+      <c r="S46" s="18" t="inlineStr">
         <is>
           <t>Only as good as the competency data, which is incomplete today. This is human work performed on information the system does not hold.</t>
         </is>
       </c>
-      <c r="S46" s="18" t="inlineStr">
+      <c r="T46" s="18" t="inlineStr">
         <is>
           <t>Would we build a competency register, and who maintains it?</t>
         </is>
@@ -5965,27 +6228,32 @@
           <t>Per visit, especially at admission</t>
         </is>
       </c>
-      <c r="O47" s="22" t="inlineStr">
+      <c r="O47" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P47" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P47" s="22" t="inlineStr">
+      <c r="Q47" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q47" s="21" t="inlineStr">
+      <c r="R47" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R47" s="18" t="inlineStr">
+      <c r="S47" s="18" t="inlineStr">
         <is>
           <t>Clinical judgment with patient-safety consequences. Recommend, never decide. Useful for triage when coverage is short.</t>
         </is>
       </c>
-      <c r="S47" s="18" t="inlineStr">
+      <c r="T47" s="18" t="inlineStr">
         <is>
           <t>Do we have any usable acuity measure today, or is it entirely judgment?</t>
         </is>
@@ -6058,27 +6326,32 @@
           <t>Slow-changing</t>
         </is>
       </c>
-      <c r="O48" s="22" t="inlineStr">
+      <c r="O48" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P48" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P48" s="22" t="inlineStr">
+      <c r="Q48" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q48" s="21" t="inlineStr">
+      <c r="R48" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R48" s="18" t="inlineStr">
+      <c r="S48" s="18" t="inlineStr">
         <is>
           <t>A documented hard gate the system should simply honour — but only once it is actually written down somewhere the system can read.</t>
         </is>
       </c>
-      <c r="S48" s="18" t="inlineStr">
+      <c r="T48" s="18" t="inlineStr">
         <is>
           <t>Where are clinician restrictions recorded today? This may be the easiest structured-data win on the sheet.</t>
         </is>
@@ -6155,27 +6428,32 @@
           <t>Per visit</t>
         </is>
       </c>
-      <c r="O49" s="22" t="inlineStr">
+      <c r="O49" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P49" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P49" s="22" t="inlineStr">
+      <c r="Q49" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q49" s="21" t="inlineStr">
+      <c r="R49" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R49" s="18" t="inlineStr">
+      <c r="S49" s="18" t="inlineStr">
         <is>
           <t>Load-bearing but invisible. Protect it explicitly rather than scoring it against efficiency.</t>
         </is>
       </c>
-      <c r="S49" s="18" t="inlineStr">
+      <c r="T49" s="18" t="inlineStr">
         <is>
           <t>How much continuity are we willing to trade for routing efficiency? A policy call, not a technical one.</t>
         </is>
@@ -6248,27 +6526,32 @@
           <t>Per cadence — typically 14 days</t>
         </is>
       </c>
-      <c r="O50" s="22" t="inlineStr">
+      <c r="O50" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P50" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P50" s="22" t="inlineStr">
+      <c r="Q50" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q50" s="21" t="inlineStr">
+      <c r="R50" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R50" s="18" t="inlineStr">
+      <c r="S50" s="18" t="inlineStr">
         <is>
           <t>Rule-based and legible.</t>
         </is>
       </c>
-      <c r="S50" s="18" t="inlineStr">
+      <c r="T50" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -6341,27 +6624,32 @@
           <t>Per visit for affected patients</t>
         </is>
       </c>
-      <c r="O51" s="22" t="inlineStr">
+      <c r="O51" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P51" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P51" s="22" t="inlineStr">
+      <c r="Q51" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q51" s="21" t="inlineStr">
+      <c r="R51" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R51" s="18" t="inlineStr">
+      <c r="S51" s="18" t="inlineStr">
         <is>
           <t>Clinical judgment with patient-safety consequences — flag it, never decide it. Also the clearest place where a rehospitalisation-risk signal would earn its keep.</t>
         </is>
       </c>
-      <c r="S51" s="18" t="inlineStr">
+      <c r="T51" s="18" t="inlineStr">
         <is>
           <t>Could clinically driven timing be flagged distinctly from preference in the record?</t>
         </is>
@@ -6434,27 +6722,32 @@
           <t>Daily, when applicable</t>
         </is>
       </c>
-      <c r="O52" s="22" t="inlineStr">
+      <c r="O52" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P52" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P52" s="22" t="inlineStr">
+      <c r="Q52" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q52" s="21" t="inlineStr">
+      <c r="R52" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R52" s="18" t="inlineStr">
+      <c r="S52" s="18" t="inlineStr">
         <is>
           <t>Partly rule, partly judgment. A system can propose the sequence and flag conflicts; the clinician confirms.</t>
         </is>
       </c>
-      <c r="S52" s="18" t="inlineStr">
+      <c r="T52" s="18" t="inlineStr">
         <is>
           <t>Are there written sequencing rules, or is this entirely clinician knowledge?</t>
         </is>
@@ -6527,27 +6820,32 @@
           <t>Per patient, continuous</t>
         </is>
       </c>
-      <c r="O53" s="22" t="inlineStr">
+      <c r="O53" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P53" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P53" s="22" t="inlineStr">
+      <c r="Q53" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q53" s="21" t="inlineStr">
+      <c r="R53" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R53" s="18" t="inlineStr">
+      <c r="S53" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. A risk score may inform priority; it may not silently reorder a clinician's day or override clinical judgment. The natural companion to acuity matching when coverage is short.</t>
         </is>
       </c>
-      <c r="S53" s="18" t="inlineStr">
+      <c r="T53" s="18" t="inlineStr">
         <is>
           <t>Is Pulse data reachable from scheduling today, and in what form?</t>
         </is>
@@ -6624,27 +6922,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O54" s="22" t="inlineStr">
+      <c r="O54" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P54" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P54" s="22" t="inlineStr">
+      <c r="Q54" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q54" s="21" t="inlineStr">
+      <c r="R54" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R54" s="18" t="inlineStr">
+      <c r="S54" s="18" t="inlineStr">
         <is>
           <t>Geometry, and safely reversible. The efficiency gain here is real rather than borrowed from someone's slack.</t>
         </is>
       </c>
-      <c r="S54" s="18" t="inlineStr">
+      <c r="T54" s="18" t="inlineStr">
         <is>
           <t>What routing data does HCHB actually use today — distance, or real drive time?</t>
         </is>
@@ -6721,27 +7024,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O55" s="22" t="inlineStr">
+      <c r="O55" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P55" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P55" s="22" t="inlineStr">
+      <c r="Q55" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q55" s="21" t="inlineStr">
+      <c r="R55" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R55" s="18" t="inlineStr">
+      <c r="S55" s="18" t="inlineStr">
         <is>
           <t>Deterministic routing maths.</t>
         </is>
       </c>
-      <c r="S55" s="18" t="inlineStr">
+      <c r="T55" s="18" t="inlineStr">
         <is>
           <t>Is mileage currently reported anywhere the branch actually looks at?</t>
         </is>
@@ -6814,27 +7122,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O56" s="22" t="inlineStr">
+      <c r="O56" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P56" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P56" s="22" t="inlineStr">
+      <c r="Q56" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q56" s="21" t="inlineStr">
+      <c r="R56" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R56" s="18" t="inlineStr">
+      <c r="S56" s="18" t="inlineStr">
         <is>
           <t>A legible skeleton pinned by tacit anchors. Propose the sequence; let the person place the anchors.</t>
         </is>
       </c>
-      <c r="S56" s="18" t="inlineStr">
+      <c r="T56" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -6911,27 +7224,32 @@
           <t>Day before the visit</t>
         </is>
       </c>
-      <c r="O57" s="22" t="inlineStr">
+      <c r="O57" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P57" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P57" s="22" t="inlineStr">
+      <c r="Q57" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q57" s="21" t="inlineStr">
+      <c r="R57" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R57" s="18" t="inlineStr">
+      <c r="S57" s="18" t="inlineStr">
         <is>
           <t>Enforceable once captured; capture is the weak point. Standardising this would move patient satisfaction and team efficiency together — and it is a visible change for clinicians.</t>
         </is>
       </c>
-      <c r="S57" s="18" t="inlineStr">
+      <c r="T57" s="18" t="inlineStr">
         <is>
           <t>Do we want to move to committed time windows, and what would that cost in flexibility?</t>
         </is>
@@ -7004,27 +7322,32 @@
           <t>As raised, and by market rule</t>
         </is>
       </c>
-      <c r="O58" s="22" t="inlineStr">
+      <c r="O58" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P58" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P58" s="22" t="inlineStr">
+      <c r="Q58" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q58" s="21" t="inlineStr">
+      <c r="R58" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R58" s="18" t="inlineStr">
+      <c r="S58" s="18" t="inlineStr">
         <is>
           <t>Numbered S-45 on 19 Aug. Where it applies the slot is removed from the route rather than flagged for override. Currently invisible to any scheduling logic, and it varies by market.</t>
         </is>
       </c>
-      <c r="S58" s="18" t="inlineStr">
+      <c r="T58" s="18" t="inlineStr">
         <is>
           <t>Which markets have safety rules today, and where are they written down?</t>
         </is>
@@ -7101,27 +7424,32 @@
           <t>Weekly</t>
         </is>
       </c>
-      <c r="O59" s="22" t="inlineStr">
+      <c r="O59" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P59" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P59" s="22" t="inlineStr">
+      <c r="Q59" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q59" s="21" t="inlineStr">
+      <c r="R59" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R59" s="18" t="inlineStr">
+      <c r="S59" s="18" t="inlineStr">
         <is>
           <t>A target, not a law. Forcing it flattens the clinician's own rhythm, which costs more than it saves.</t>
         </is>
       </c>
-      <c r="S59" s="18" t="inlineStr">
+      <c r="T59" s="18" t="inlineStr">
         <is>
           <t>Is 42% by Tuesday the standard we want to hold branches to?</t>
         </is>
@@ -7198,27 +7526,32 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="O60" s="22" t="inlineStr">
+      <c r="O60" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P60" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P60" s="22" t="inlineStr">
+      <c r="Q60" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q60" s="21" t="inlineStr">
+      <c r="R60" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R60" s="18" t="inlineStr">
+      <c r="S60" s="18" t="inlineStr">
         <is>
           <t>A derived read, safe to surface. This is the archetype of the pattern you described: the system can produce it, but somebody has to look and act.</t>
         </is>
       </c>
-      <c r="S60" s="18" t="inlineStr">
+      <c r="T60" s="18" t="inlineStr">
         <is>
           <t>Who should own the daily pace read — Clinical Manager, Scheduler, or both?</t>
         </is>
@@ -7295,27 +7628,32 @@
           <t>Weekly</t>
         </is>
       </c>
-      <c r="O61" s="22" t="inlineStr">
+      <c r="O61" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P61" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P61" s="22" t="inlineStr">
+      <c r="Q61" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q61" s="21" t="inlineStr">
+      <c r="R61" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R61" s="18" t="inlineStr">
+      <c r="S61" s="18" t="inlineStr">
         <is>
           <t>Optimisable, but it touches human routines — assist rather than dictate.</t>
         </is>
       </c>
-      <c r="S61" s="18" t="inlineStr">
+      <c r="T61" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -7392,27 +7730,32 @@
           <t>On event</t>
         </is>
       </c>
-      <c r="O62" s="22" t="inlineStr">
+      <c r="O62" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P62" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P62" s="22" t="inlineStr">
+      <c r="Q62" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q62" s="21" t="inlineStr">
+      <c r="R62" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R62" s="18" t="inlineStr">
+      <c r="S62" s="18" t="inlineStr">
         <is>
           <t>Sensing the miss is legible; the recovery pulls the whole problem back in. Note the visit states run scheduled, then documentation pending, then missed — so 'missed' is a late signal.</t>
         </is>
       </c>
-      <c r="S62" s="18" t="inlineStr">
+      <c r="T62" s="18" t="inlineStr">
         <is>
           <t>Can we detect a likely miss earlier than the missed status appears?</t>
         </is>
@@ -7485,27 +7828,32 @@
           <t>On event</t>
         </is>
       </c>
-      <c r="O63" s="22" t="inlineStr">
+      <c r="O63" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="P63" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P63" s="22" t="inlineStr">
+      <c r="Q63" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q63" s="21" t="inlineStr">
+      <c r="R63" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R63" s="18" t="inlineStr">
+      <c r="S63" s="18" t="inlineStr">
         <is>
           <t>Workflow and compliance prompting — safe to automate, and already partly automated.</t>
         </is>
       </c>
-      <c r="S63" s="18" t="inlineStr">
+      <c r="T63" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -7582,27 +7930,32 @@
           <t>Continuous</t>
         </is>
       </c>
-      <c r="O64" s="22" t="inlineStr">
+      <c r="O64" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
+      <c r="P64" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P64" s="22" t="inlineStr">
+      <c r="Q64" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q64" s="21" t="inlineStr">
+      <c r="R64" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R64" s="18" t="inlineStr">
+      <c r="S64" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and it constrains the whole design: nothing may depend on real-time visit state read out of HCHB. The workbook's example is stark — a clinician who called an ambulance has started a visit that did not happen, and the schedule still reads as worked.</t>
         </is>
       </c>
-      <c r="S64" s="18" t="inlineStr">
+      <c r="T64" s="18" t="inlineStr">
         <is>
           <t>How long is the blind window in practice? Nobody has measured it.</t>
         </is>
@@ -7611,242 +7964,252 @@
     <row r="65" ht="76" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>CO-09</t>
-        </is>
-      </c>
-      <c r="B65" s="24" t="inlineStr">
-        <is>
-          <t>Scheduling Engine</t>
+          <t>S-25</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>Patient Engagement</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Patient Engagement</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
         <is>
-          <t>Finding coverage when someone calls out</t>
+          <t>Times the patient will not accept</t>
         </is>
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>The scramble when a clinician is out. It is owned jointly by the DCS and the scheduler, and it runs on who will actually say yes — calls, texts and Teams messages to full-time and per-diem staff, then reassignment or moving the visit to another day.</t>
+          <t>A flat refusal of a time band — nothing before eleven, no afternoons. It removes slots outright and reshapes the whole route around it.</t>
         </is>
       </c>
       <c r="H65" s="20" t="inlineStr">
         <is>
-          <t>DCS and Scheduler — jointly</t>
+          <t>Scheduler or Clinician — captures it in conversation</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>DCS and Scheduler — jointly; DCS escalates for a start of care</t>
+          <t>Scheduler — schedules around it</t>
         </is>
       </c>
       <c r="J65" s="20" t="inlineStr">
         <is>
-          <t>No system holds this. It runs on phone, text and Teams, against the scheduler's knowledge of who might take it.</t>
+          <t>HCHB coordination note — free text written by a person, not a structured field.</t>
         </is>
       </c>
       <c r="K65" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L65" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M65" s="20" t="inlineStr">
         <is>
-          <t>DCS and Scheduler — jointly</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
-          <t>On event</t>
-        </is>
-      </c>
-      <c r="O65" s="22" t="inlineStr">
+          <t>Per episode, revisited in conversation</t>
+        </is>
+      </c>
+      <c r="O65" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P65" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P65" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q65" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R65" s="18" t="inlineStr">
-        <is>
-          <t>Runs on the same relational willingness as the per-diem and elasticity rows. A system can assemble the candidate list and reach people directly; it cannot decide who will say yes. This is where an incentive on a hard-to-fill visit would attach.</t>
+      <c r="Q65" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R65" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S65" s="18" t="inlineStr">
         <is>
-          <t>Would we let the system contact clinicians directly with an open visit, or must a person always make the ask?</t>
+          <t>Hard once captured, but a stale refusal causes a failed visit — and in practice these soften with relationship. Worth re-testing rather than treating as permanent.</t>
+        </is>
+      </c>
+      <c r="T65" s="18" t="inlineStr">
+        <is>
+          <t>Should refusals carry a review date so they do not calcify?</t>
         </is>
       </c>
     </row>
     <row r="66" ht="76" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>CO-10</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>Scheduling Engine</t>
+          <t>S-26</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Patient Engagement</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>Across the care team</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Patient Engagement</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>Coordinating visits across disciplines</t>
+          <t>Preferred visit window</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
-          <t>Spacing the nurse, the therapist and the aide sensibly across a week rather than stacking two on one day and leaving the patient idle the next.</t>
+          <t>When the patient would like to be seen. Softer than a refusal, but it drives satisfaction and whether the visit actually happens.</t>
         </is>
       </c>
       <c r="H66" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — spaces them; Clinician — adjusts</t>
+          <t>Scheduler or Clinician — captures it</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
+          <t>Scheduler — optimises toward it</t>
+        </is>
+      </c>
+      <c r="J66" s="20" t="inlineStr">
+        <is>
+          <t>HCHB coordination note — free text.</t>
+        </is>
+      </c>
+      <c r="K66" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
+      <c r="M66" s="20" t="inlineStr">
+        <is>
           <t>Scheduler</t>
         </is>
       </c>
-      <c r="J66" s="20" t="inlineStr">
-        <is>
-          <t>HCHB holds the visits; the spacing judgment is manual.</t>
-        </is>
-      </c>
-      <c r="K66" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L66" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M66" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
-          <t>Weekly per patient</t>
-        </is>
-      </c>
-      <c r="O66" s="22" t="inlineStr">
+          <t>Per episode</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P66" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P66" s="22" t="inlineStr">
+      <c r="Q66" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q66" s="21" t="inlineStr">
+      <c r="R66" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R66" s="18" t="inlineStr">
-        <is>
-          <t>Rule-informed but bounded by what a patient will tolerate in a week. Propose, do not dictate.</t>
-        </is>
-      </c>
       <c r="S66" s="18" t="inlineStr">
         <is>
-          <t>Is there a standard on how many visits a patient should have in one day?</t>
+          <t>Optimise toward it, confirm before committing.</t>
+        </is>
+      </c>
+      <c r="T66" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="76" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>CO-11</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>Scheduling Engine</t>
+          <t>S-27</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Patient Engagement</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr"/>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>Across the care team</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Patient Engagement</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
         <is>
-          <t>Keeping the team and the office in step</t>
+          <t>Days the patient is committed elsewhere</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t>The connective work of telling the case manager and the office when something changes. Today it is the coordination-note habit — and how well it works depends entirely on people remembering.</t>
+          <t>Standing commitments that block whole days — dialysis on Monday, Wednesday and Friday, a regular clinic appointment. These are hard, and they are patient-reported.</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Scheduler and Clinician — write the notes</t>
+          <t>Scheduler or Clinician — captures it</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Case Manager / Clinical Manager — act on what they read</t>
+          <t>Scheduler — schedules around it</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination notes.</t>
+          <t>HCHB coordination note — free text.</t>
         </is>
       </c>
       <c r="K67" s="21" t="inlineStr">
@@ -7861,94 +8224,99 @@
       </c>
       <c r="M67" s="20" t="inlineStr">
         <is>
-          <t>Clinical Manager</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="O67" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
+          <t>Per episode</t>
+        </is>
+      </c>
+      <c r="O67" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P67" s="22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q67" s="21" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q67" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R67" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R67" s="18" t="inlineStr">
-        <is>
-          <t>Logging and notifying is automatable; deciding what deserves an escalation is human judgment.</t>
-        </is>
-      </c>
       <c r="S67" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding.</t>
+          <t>A standing constraint, but patient-reported — trust and verify.</t>
+        </is>
+      </c>
+      <c r="T67" s="18" t="inlineStr">
+        <is>
+          <t>Could standing commitments be captured as structured dates rather than free text?</t>
         </is>
       </c>
     </row>
     <row r="68" ht="76" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>CO-12</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>Scheduling Engine</t>
+          <t>S-28</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Patient Engagement</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>Across the care team</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Patient Engagement</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>What coordination actually costs</t>
+          <t>Caregiver has to be present</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>The time clinicians and schedulers spend on coordination rather than care. It is capacity, and today it is invisible — roughly forty-five minutes a day per clinician by one estimate, which is a visit.</t>
+          <t>Some visits can only happen when a family member or carer is there — wound-care teaching, insulin, or simply to let the clinician in. It ties the visit to a second person's calendar.</t>
         </is>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
-          <t>Everyone — it is spread across every role</t>
+          <t>Scheduler or Clinician — confirms before booking</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>— no one measures it today</t>
+          <t>Scheduler — and the Clinician on the day</t>
         </is>
       </c>
       <c r="J68" s="20" t="inlineStr">
         <is>
-          <t>Not measured anywhere.</t>
+          <t>HCHB coordination note — free text.</t>
         </is>
       </c>
       <c r="K68" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
@@ -7958,44 +8326,49 @@
       </c>
       <c r="M68" s="20" t="inlineStr">
         <is>
-          <t>Clinical Manager / Branch Leadership — to act on the trend</t>
+          <t>Scheduler — confirms with the family</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="O68" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
+          <t>Per visit for affected patients</t>
+        </is>
+      </c>
+      <c r="O68" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P68" s="22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q68" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R68" s="18" t="inlineStr">
-        <is>
-          <t>Measure and surface it; do not try to control the people doing it. This is the number that turns the business case from theory into a figure the branch recognises.</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q68" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R68" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S68" s="18" t="inlineStr">
         <is>
-          <t>Is there an appetite to measure this directly, or should it be estimated from the automation we remove?</t>
+          <t>The clearest 'surface, never decide' row on the sheet: a hard rule, a changing informal input, and a patient-safety consequence if it is wrong.</t>
+        </is>
+      </c>
+      <c r="T68" s="18" t="inlineStr">
+        <is>
+          <t>How often does caregiver availability change mid-episode, and does anyone update the note when it does?</t>
         </is>
       </c>
     </row>
     <row r="69" ht="76" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>S-25</t>
+          <t>S-29</t>
         </is>
       </c>
       <c r="B69" s="25" t="inlineStr">
@@ -8020,27 +8393,27 @@
       </c>
       <c r="F69" s="18" t="inlineStr">
         <is>
-          <t>Times the patient will not accept</t>
+          <t>Cognitive and dementia constraints</t>
         </is>
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t>A flat refusal of a time band — nothing before eleven, no afternoons. It removes slots outright and reshapes the whole route around it.</t>
+          <t>When a patient cannot safely admit a clinician or follow instruction alone, a caregiver becomes a hard gate and the available windows narrow sharply.</t>
         </is>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>Scheduler or Clinician — captures it in conversation</t>
+          <t>Clinician — identifies it; Scheduler — schedules to it</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — schedules around it</t>
+          <t>Clinician — owns the clinical judgment</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination note — free text written by a person, not a structured field.</t>
+          <t>Clinical detail in HCHB; the scheduling consequence in the coordination note.</t>
         </is>
       </c>
       <c r="K69" s="21" t="inlineStr">
@@ -8050,49 +8423,54 @@
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="M69" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinician / Clinical Manager</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>Per episode, revisited in conversation</t>
-        </is>
-      </c>
-      <c r="O69" s="22" t="inlineStr">
+          <t>Per episode</t>
+        </is>
+      </c>
+      <c r="O69" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P69" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P69" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q69" s="21" t="inlineStr">
+      <c r="Q69" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R69" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R69" s="18" t="inlineStr">
-        <is>
-          <t>Hard once captured, but a stale refusal causes a failed visit — and in practice these soften with relationship. Worth re-testing rather than treating as permanent.</t>
-        </is>
-      </c>
       <c r="S69" s="18" t="inlineStr">
         <is>
-          <t>Should refusals carry a review date so they do not calcify?</t>
+          <t>Cognition plus caregiver dependency plus safety. Automation must only surface.</t>
+        </is>
+      </c>
+      <c r="T69" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding — but confirm the note reliably reaches the scheduler.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="76" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>S-26</t>
+          <t>S-30</t>
         </is>
       </c>
       <c r="B70" s="25" t="inlineStr">
@@ -8117,79 +8495,84 @@
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>Preferred visit window</t>
+          <t>The caregiver's own changing schedule</t>
         </is>
       </c>
       <c r="G70" s="18" t="inlineStr">
         <is>
-          <t>When the patient would like to be seen. Softer than a refusal, but it drives satisfaction and whether the visit actually happens.</t>
+          <t>Scheduling around two moving calendars at once — the patient's and a carer who works rotating shifts. The hardest real case in the whole model, and almost entirely undocumented.</t>
         </is>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
-          <t>Scheduler or Clinician — captures it</t>
+          <t>Scheduler and Clinician — renegotiate as it changes</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — optimises toward it</t>
+          <t>Scheduler — with the family</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination note — free text.</t>
+          <t>Not recorded anywhere in a durable form.</t>
         </is>
       </c>
       <c r="K70" s="21" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="M70" s="20" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
+        <is>
+          <t>Weekly, sometimes more</t>
+        </is>
+      </c>
+      <c r="O70" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P70" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q70" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R70" s="21" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M70" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
-        <is>
-          <t>Per episode</t>
-        </is>
-      </c>
-      <c r="O70" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
-        </is>
-      </c>
-      <c r="P70" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q70" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R70" s="18" t="inlineStr">
-        <is>
-          <t>Optimise toward it, confirm before committing.</t>
-        </is>
-      </c>
       <c r="S70" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding.</t>
+          <t>Two undocumented moving calendars. A system can show what it last heard; it cannot know.</t>
+        </is>
+      </c>
+      <c r="T70" s="18" t="inlineStr">
+        <is>
+          <t>Is there any value in capturing caregiver availability as structured data, or is it too volatile to be worth it?</t>
         </is>
       </c>
     </row>
     <row r="71" ht="76" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>S-27</t>
+          <t>S-32</t>
         </is>
       </c>
       <c r="B71" s="25" t="inlineStr">
@@ -8197,7 +8580,11 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr"/>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Matching</t>
@@ -8210,27 +8597,27 @@
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>Days the patient is committed elsewhere</t>
+          <t>Competing medical appointments</t>
         </is>
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>Standing commitments that block whole days — dialysis on Monday, Wednesday and Friday, a regular clinic appointment. These are hard, and they are patient-reported.</t>
+          <t>The patient's other appointments — dialysis, infusion, a specialist visit — that remove days or windows. Usually surfaces in conversation rather than in the record.</t>
         </is>
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>Scheduler or Clinician — captures it</t>
+          <t>Scheduler or Clinician — learns it by asking</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — schedules around it</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination note — free text.</t>
+          <t>HCHB coordination note when captured; otherwise not recorded.</t>
         </is>
       </c>
       <c r="K71" s="21" t="inlineStr">
@@ -8250,39 +8637,44 @@
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>Per episode</t>
-        </is>
-      </c>
-      <c r="O71" s="22" t="inlineStr">
+          <t>Per episode, and it changes</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P71" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P71" s="22" t="inlineStr">
+      <c r="Q71" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q71" s="21" t="inlineStr">
+      <c r="R71" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R71" s="18" t="inlineStr">
-        <is>
-          <t>A standing constraint, but patient-reported — trust and verify.</t>
-        </is>
-      </c>
       <c r="S71" s="18" t="inlineStr">
         <is>
-          <t>Could standing commitments be captured as structured dates rather than free text?</t>
+          <t>Capturable if reported. The failure mode is a visit booked into an appointment nobody knew about.</t>
+        </is>
+      </c>
+      <c r="T71" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="76" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>S-28</t>
+          <t>S-23</t>
         </is>
       </c>
       <c r="B72" s="25" t="inlineStr">
@@ -8290,11 +8682,7 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="C72" s="18" t="inlineStr"/>
       <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Matching</t>
@@ -8307,22 +8695,22 @@
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>Caregiver has to be present</t>
+          <t>Gender preference</t>
         </is>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t>Some visits can only happen when a family member or carer is there — wound-care teaching, insulin, or simply to let the clinician in. It ties the visit to a second person's calendar.</t>
+          <t>A patient's request for a clinician of a particular gender, often for cultural, religious or comfort reasons — and effectively hard when it applies to personal care.</t>
         </is>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>Scheduler or Clinician — confirms before booking</t>
+          <t>Scheduler — captures and matches</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — and the Clinician on the day</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
@@ -8337,49 +8725,54 @@
       </c>
       <c r="L72" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M72" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — confirms with the family</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>Per visit for affected patients</t>
-        </is>
-      </c>
-      <c r="O72" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Per episode</t>
+        </is>
+      </c>
+      <c r="O72" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P72" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q72" s="21" t="inlineStr">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q72" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R72" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R72" s="18" t="inlineStr">
-        <is>
-          <t>The clearest 'surface, never decide' row on the sheet: a hard rule, a changing informal input, and a patient-safety consequence if it is wrong.</t>
-        </is>
-      </c>
       <c r="S72" s="18" t="inlineStr">
         <is>
-          <t>How often does caregiver availability change mid-episode, and does anyone update the note when it does?</t>
+          <t>Sensitive. Surface and confirm rather than auto-matching on it.</t>
+        </is>
+      </c>
+      <c r="T72" s="18" t="inlineStr">
+        <is>
+          <t>Is there a policy on how this is recorded and honoured?</t>
         </is>
       </c>
     </row>
     <row r="73" ht="76" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>S-29</t>
+          <t>S-24</t>
         </is>
       </c>
       <c r="B73" s="25" t="inlineStr">
@@ -8404,42 +8797,42 @@
       </c>
       <c r="F73" s="18" t="inlineStr">
         <is>
-          <t>Cognitive and dementia constraints</t>
+          <t>Language and cultural match</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>When a patient cannot safely admit a clinician or follow instruction alone, a caregiver becomes a hard gate and the available windows narrow sharply.</t>
+          <t>Pairing a patient with a clinician who shares their language where possible. It materially affects teaching visits, where the whole point is that the patient understands.</t>
         </is>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Clinician — identifies it; Scheduler — schedules to it</t>
+          <t>Scheduler — matches where they can</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Clinician — owns the clinical judgment</t>
+          <t>Scheduler; Clinician — raises it when teaching fails</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>Clinical detail in HCHB; the scheduling consequence in the coordination note.</t>
+          <t>Languages spoken are not reliably recorded for clinicians; patient language is in HCHB.</t>
         </is>
       </c>
       <c r="K73" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M73" s="20" t="inlineStr">
         <is>
-          <t>Clinician / Clinical Manager</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
@@ -8447,36 +8840,41 @@
           <t>Per episode</t>
         </is>
       </c>
-      <c r="O73" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="O73" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P73" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q73" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R73" s="18" t="inlineStr">
-        <is>
-          <t>Cognition plus caregiver dependency plus safety. Automation must only surface.</t>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q73" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R73" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S73" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding — but confirm the note reliably reaches the scheduler.</t>
+          <t>Capturable on both sides, and worth confirming specifically for teaching-critical visits.</t>
+        </is>
+      </c>
+      <c r="T73" s="18" t="inlineStr">
+        <is>
+          <t>Do we hold clinician language capability anywhere today?</t>
         </is>
       </c>
     </row>
     <row r="74" ht="76" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>S-30</t>
+          <t>CO-04</t>
         </is>
       </c>
       <c r="B74" s="25" t="inlineStr">
@@ -8484,54 +8882,50 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="C74" s="18" t="inlineStr"/>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>The caregiver's own changing schedule</t>
+          <t>New-patient welcome call</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>Scheduling around two moving calendars at once — the patient's and a carer who works rotating shifts. The hardest real case in the whole model, and almost entirely undocumented.</t>
+          <t>The first call to a newly referred patient. Today it carries a real judgment as well as a greeting: is the patient actually home, or still in hospital, or putting admission off? It happens before anyone is sent out, which is precisely why nobody is sent to an empty house.</t>
         </is>
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>Scheduler and Clinician — renegotiate as it changes</t>
+          <t>Scheduler — makes the call</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — with the family</t>
+          <t>Scheduler — makes the one true judgment call in the current process</t>
         </is>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>Not recorded anywhere in a durable form.</t>
+          <t>HCHB — the visit and the coordination note that follows.</t>
         </is>
       </c>
       <c r="K74" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M74" s="20" t="inlineStr">
@@ -8541,39 +8935,44 @@
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>Weekly, sometimes more</t>
-        </is>
-      </c>
-      <c r="O74" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Per referral</t>
+        </is>
+      </c>
+      <c r="O74" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
         </is>
       </c>
       <c r="P74" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q74" s="21" t="inlineStr">
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q74" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R74" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R74" s="18" t="inlineStr">
-        <is>
-          <t>Two undocumented moving calendars. A system can show what it last heard; it cannot know.</t>
-        </is>
-      </c>
       <c r="S74" s="18" t="inlineStr">
         <is>
-          <t>Is there any value in capturing caregiver availability as structured data, or is it too volatile to be worth it?</t>
+          <t>Automate the trigger and the routine parts; keep a person on the line for the judgment. This is the highest-value human call in the admission chain.</t>
+        </is>
+      </c>
+      <c r="T74" s="18" t="inlineStr">
+        <is>
+          <t>If outreach is automated, how do we preserve the 'is the patient really home' check?</t>
         </is>
       </c>
     </row>
     <row r="75" ht="76" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>S-32</t>
+          <t>CO-06</t>
         </is>
       </c>
       <c r="B75" s="25" t="inlineStr">
@@ -8583,32 +8982,32 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="inlineStr">
-        <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
       <c r="F75" s="18" t="inlineStr">
         <is>
-          <t>Competing medical appointments</t>
+          <t>Confirming availability before booking</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t>The patient's other appointments — dialysis, infusion, a specialist visit — that remove days or windows. Usually surfaces in conversation rather than in the record.</t>
+          <t>Checking the patient — and where needed the caregiver — can actually make a slot before it is committed. It prevents booking into a window that was always going to fail.</t>
         </is>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>Scheduler or Clinician — learns it by asking</t>
+          <t>Scheduler — confirms</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
@@ -8618,59 +9017,64 @@
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination note when captured; otherwise not recorded.</t>
+          <t>Not systematically recorded; the confirmation happens in conversation.</t>
         </is>
       </c>
       <c r="K75" s="21" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L75" s="20" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="M75" s="20" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>Per visit at booking</t>
+        </is>
+      </c>
+      <c r="O75" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P75" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q75" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R75" s="21" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L75" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M75" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>Per episode, and it changes</t>
-        </is>
-      </c>
-      <c r="O75" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P75" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q75" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R75" s="18" t="inlineStr">
-        <is>
-          <t>Capturable if reported. The failure mode is a visit booked into an appointment nobody knew about.</t>
-        </is>
-      </c>
       <c r="S75" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding.</t>
+          <t>Feeds directly off the caregiver-availability rows, which are the least reliable data on the sheet. Surface what is known; do not presume it is current.</t>
+        </is>
+      </c>
+      <c r="T75" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding — but this row depends on S-28 and S-30 being right.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="76" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>S-23</t>
+          <t>CO-01</t>
         </is>
       </c>
       <c r="B76" s="25" t="inlineStr">
@@ -8678,92 +9082,101 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr"/>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="E76" s="23" t="inlineStr">
-        <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>Gender preference</t>
+          <t>Day-before confirmation</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t>A patient's request for a clinician of a particular gender, often for cultural, religious or comfort reasons — and effectively hard when it applies to personal care.</t>
+          <t>The call that confirms tomorrow's visit will actually happen. It is the single biggest reducer of failed visits — and today every clinician does it by hand, for every patient, every day. The system sends nothing.</t>
         </is>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — captures and matches</t>
+          <t>Clinician — calls or texts each patient the evening before</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinician — and picks the disposition straight afterwards</t>
         </is>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>HCHB coordination note — free text.</t>
+          <t>The call is not recorded. Its outcome shows up as the disposition selected in HCHB.</t>
         </is>
       </c>
       <c r="K76" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Automate</t>
         </is>
       </c>
       <c r="M76" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinician — takes over when the automated round surfaces a problem</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
-          <t>Per episode</t>
-        </is>
-      </c>
-      <c r="O76" s="22" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Daily, day before</t>
+        </is>
+      </c>
+      <c r="O76" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
         </is>
       </c>
       <c r="P76" s="22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q76" s="22" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q76" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R76" s="18" t="inlineStr">
-        <is>
-          <t>Sensitive. Surface and confirm rather than auto-matching on it.</t>
+      <c r="R76" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="S76" s="18" t="inlineStr">
         <is>
-          <t>Is there a policy on how this is recorded and honoured?</t>
+          <t>The largest single block of clinician time this initiative can hand back. The one-pager now commits to automating the round and to keeping the schedule pliable until confirmation, so changes can land before the patient is told. The care in the design is that the call also surfaces things a reminder never would.</t>
+        </is>
+      </c>
+      <c r="T76" s="18" t="inlineStr">
+        <is>
+          <t>How do we automate the round without losing what the conversation catches?</t>
         </is>
       </c>
     </row>
     <row r="77" ht="76" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>S-24</t>
+          <t>CO-02</t>
         </is>
       </c>
       <c r="B77" s="25" t="inlineStr">
@@ -8771,96 +9184,97 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
+      <c r="C77" s="18" t="inlineStr"/>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>Matching</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="inlineStr">
-        <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
         <is>
-          <t>Language and cultural match</t>
+          <t>Automated reminders</t>
         </is>
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>Pairing a patient with a clinician who shares their language where possible. It materially affects teaching visits, where the whole point is that the patient understands.</t>
+          <t>System-sent reminders ahead of a visit. A clean, low-risk automation that reduces no-shows without consuming anyone's time — and one Homecare Homebase does not do today.</t>
         </is>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — matches where they can</t>
+          <t>— nobody; this does not happen today</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Scheduler; Clinician — raises it when teaching fails</t>
+          <t>— no one today; this does not happen</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>Languages spoken are not reliably recorded for clinicians; patient language is in HCHB.</t>
+          <t>Does not exist today. Would need an outbound channel.</t>
         </is>
       </c>
       <c r="K77" s="21" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>Automate</t>
+        </is>
+      </c>
+      <c r="M77" s="20" t="inlineStr">
+        <is>
+          <t>— exception only</t>
+        </is>
+      </c>
+      <c r="N77" s="20" t="inlineStr">
+        <is>
+          <t>Per visit</t>
+        </is>
+      </c>
+      <c r="O77" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P77" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q77" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R77" s="21" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L77" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M77" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="N77" s="20" t="inlineStr">
-        <is>
-          <t>Per episode</t>
-        </is>
-      </c>
-      <c r="O77" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
-        </is>
-      </c>
-      <c r="P77" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q77" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R77" s="18" t="inlineStr">
-        <is>
-          <t>Capturable on both sides, and worth confirming specifically for teaching-critical visits.</t>
-        </is>
-      </c>
       <c r="S77" s="18" t="inlineStr">
         <is>
-          <t>Do we hold clinician language capability anywhere today?</t>
+          <t>Deterministic and safe. This is the most obvious quick win in the engagement arena.</t>
+        </is>
+      </c>
+      <c r="T77" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="76" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>CO-04</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="B78" s="25" t="inlineStr">
@@ -8881,79 +9295,84 @@
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>New-patient welcome call</t>
+          <t>On-my-way notification</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>The first call to a newly referred patient. Today it carries a real judgment as well as a greeting: is the patient actually home, or still in hospital, or putting admission off? It happens before anyone is sent out, which is precisely why nobody is sent to an empty house.</t>
+          <t>Telling the patient the clinician is roughly twenty minutes out. It is fully derivable from the live route and it materially changes the experience of waiting.</t>
         </is>
       </c>
       <c r="H78" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — makes the call</t>
+          <t>— nobody; this does not happen today</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — makes the one true judgment call in the current process</t>
+          <t>— no one today; this does not happen</t>
         </is>
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
-          <t>HCHB — the visit and the coordination note that follows.</t>
+          <t>Does not exist today. Would derive from route and position.</t>
         </is>
       </c>
       <c r="K78" s="21" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
+        <is>
+          <t>Automate</t>
+        </is>
+      </c>
+      <c r="M78" s="20" t="inlineStr">
+        <is>
+          <t>— exception only</t>
+        </is>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>Per visit</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P78" s="22" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q78" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R78" s="21" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L78" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M78" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>Per referral</t>
-        </is>
-      </c>
-      <c r="O78" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
-        </is>
-      </c>
-      <c r="P78" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q78" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R78" s="18" t="inlineStr">
-        <is>
-          <t>Automate the trigger and the routine parts; keep a person on the line for the judgment. This is the highest-value human call in the admission chain.</t>
-        </is>
-      </c>
       <c r="S78" s="18" t="inlineStr">
         <is>
-          <t>If outreach is automated, how do we preserve the 'is the patient really home' check?</t>
+          <t>Deterministic from position and route. Note it implies clinician location tracking, which is a conversation to have deliberately.</t>
+        </is>
+      </c>
+      <c r="T78" s="18" t="inlineStr">
+        <is>
+          <t>Are we comfortable with the location tracking this implies, and have clinicians been consulted?</t>
         </is>
       </c>
     </row>
     <row r="79" ht="76" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>CO-06</t>
+          <t>CO-05</t>
         </is>
       </c>
       <c r="B79" s="25" t="inlineStr">
@@ -8961,11 +9380,7 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
-        <is>
-          <t>Scheduling</t>
-        </is>
-      </c>
+      <c r="C79" s="18" t="inlineStr"/>
       <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Before the visit</t>
@@ -8978,17 +9393,17 @@
       </c>
       <c r="F79" s="18" t="inlineStr">
         <is>
-          <t>Confirming availability before booking</t>
+          <t>Channel and communication preferences</t>
         </is>
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>Checking the patient — and where needed the caregiver — can actually make a slot before it is committed. It prevents booking into a window that was always going to fail.</t>
+          <t>How each patient wants to be reached — text, call or email — and what they have consented to. It decides whether any of the automation above actually lands.</t>
         </is>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — confirms</t>
+          <t>Scheduler — captures it when it comes up</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
@@ -8998,7 +9413,7 @@
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>Not systematically recorded; the confirmation happens in conversation.</t>
+          <t>Phone numbers are in HCHB. Channel preference and consent are not systematically held.</t>
         </is>
       </c>
       <c r="K79" s="21" t="inlineStr">
@@ -9008,7 +9423,7 @@
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M79" s="20" t="inlineStr">
@@ -9018,39 +9433,44 @@
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>Per visit at booking</t>
-        </is>
-      </c>
-      <c r="O79" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Per episode</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P79" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q79" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R79" s="18" t="inlineStr">
-        <is>
-          <t>Feeds directly off the caregiver-availability rows, which are the least reliable data on the sheet. Surface what is known; do not presume it is current.</t>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q79" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R79" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S79" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding — but this row depends on S-28 and S-30 being right.</t>
+          <t>Honour it, never assume it. Conflict risk: a vendor with its own communication model may not respect an existing preference store. Consent and opt-out rules also carry regulatory weight.</t>
+        </is>
+      </c>
+      <c r="T79" s="18" t="inlineStr">
+        <is>
+          <t>Where would channel preference and consent live, and who captures it at admission?</t>
         </is>
       </c>
     </row>
     <row r="80" ht="76" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>CO-01</t>
+          <t>S-47</t>
         </is>
       </c>
       <c r="B80" s="25" t="inlineStr">
@@ -9060,7 +9480,7 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
@@ -9075,79 +9495,84 @@
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Day-before confirmation</t>
+          <t>Power of attorney and who can sign</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>The call that confirms tomorrow's visit will actually happen. It is the single biggest reducer of failed visits — and today every clinician does it by hand, for every patient, every day. The system sends nothing.</t>
+          <t>Whether someone other than the patient holds legal authority to sign admission consents and to be the contact of record. Where a power of attorney exists the patient's own agreement does not satisfy consent, and some direct that the patient not be contacted at all.</t>
         </is>
       </c>
       <c r="H80" s="20" t="inlineStr">
         <is>
-          <t>Clinician — calls or texts each patient the evening before</t>
+          <t>Intake and Scheduler — capture it if it surfaces</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Clinician — and picks the disposition straight afterwards</t>
+          <t>Scheduler — decides who to contact</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>The call is not recorded. Its outcome shows up as the disposition selected in HCHB.</t>
+          <t>Partly Commure at referral, otherwise manual. Not reliably known before the visit is booked.</t>
         </is>
       </c>
       <c r="K80" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>Automate</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M80" s="20" t="inlineStr">
         <is>
-          <t>Clinician — takes over when the automated round surfaces a problem</t>
+          <t>Scheduler — confirms who may be contacted</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>Daily, day before</t>
-        </is>
-      </c>
-      <c r="O80" s="22" t="inlineStr">
+          <t>Per referral, before booking</t>
+        </is>
+      </c>
+      <c r="O80" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P80" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P80" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q80" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R80" s="18" t="inlineStr">
-        <is>
-          <t>The largest single block of clinician time this initiative can hand back. The one-pager now commits to automating the round and to keeping the schedule pliable until confirmation, so changes can land before the patient is told. The care in the design is that the call also surfaces things a reminder never would.</t>
+      <c r="Q80" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R80" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S80" s="18" t="inlineStr">
         <is>
-          <t>How do we automate the round without losing what the conversation catches?</t>
+          <t>Added 19 Aug. The failure it prevents is concrete: a nurse arrives for the start of care, the patient cannot sign, and the power of attorney is two states away. The visit is wasted and the clock keeps running.</t>
+        </is>
+      </c>
+      <c r="T80" s="18" t="inlineStr">
+        <is>
+          <t>Where would POA status be captured so the scheduler sees it before booking rather than after?</t>
         </is>
       </c>
     </row>
     <row r="81" ht="76" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>CO-02</t>
+          <t>CO-13</t>
         </is>
       </c>
       <c r="B81" s="25" t="inlineStr">
@@ -9168,32 +9593,32 @@
       </c>
       <c r="F81" s="18" t="inlineStr">
         <is>
-          <t>Automated reminders</t>
+          <t>A verified number for the right person</t>
         </is>
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>System-sent reminders ahead of a visit. A clean, low-risk automation that reduces no-shows without consuming anyone's time — and one Homecare Homebase does not do today.</t>
+          <t>The confirmed phone number and reachable channel for the patient and, where it applies, the caregiver or power of attorney — including which of them is the right person to talk to about scheduling. Every piece of coordination depends on this, and today it is scattered.</t>
         </is>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>— nobody; this does not happen today</t>
+          <t>Intake and Scheduler — capture what they are given</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>— no one today; this does not happen</t>
+          <t>Scheduler — works out who to call</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>Does not exist today. Would need an outbound channel.</t>
+          <t>Partly HCHB, partly Commure, partly neither. There is no single verified record.</t>
         </is>
       </c>
       <c r="K81" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
@@ -9203,44 +9628,49 @@
       </c>
       <c r="M81" s="20" t="inlineStr">
         <is>
-          <t>— exception only</t>
+          <t>Scheduler — owns the exception when nobody answers</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>Per visit</t>
-        </is>
-      </c>
-      <c r="O81" s="22" t="inlineStr">
+          <t>Per referral, verified at admission</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
+      <c r="P81" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P81" s="22" t="inlineStr">
+      <c r="Q81" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q81" s="21" t="inlineStr">
+      <c r="R81" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R81" s="18" t="inlineStr">
-        <is>
-          <t>Deterministic and safe. This is the most obvious quick win in the engagement arena.</t>
-        </is>
-      </c>
       <c r="S81" s="18" t="inlineStr">
         <is>
-          <t>Nothing outstanding.</t>
+          <t>Added 19 Aug, and distinct from channel preference: a preference is no use without a working number for the right party. The failure it names is reminders going to a disconnected mobile while the daughter who books every visit is never contacted.</t>
+        </is>
+      </c>
+      <c r="T81" s="18" t="inlineStr">
+        <is>
+          <t>Who verifies the number, and at what point in admission?</t>
         </is>
       </c>
     </row>
     <row r="82" ht="76" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>CO-03</t>
+          <t>CO-14</t>
         </is>
       </c>
       <c r="B82" s="25" t="inlineStr">
@@ -9261,32 +9691,32 @@
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>On-my-way notification</t>
+          <t>Consent to contact, by channel</t>
         </is>
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>Telling the patient the clinician is roughly twenty minutes out. It is fully derivable from the live route and it materially changes the experience of waiting.</t>
+          <t>Which channels we are legally allowed to use — texting, and sharing information with family — and whether the consent has actually been signed. A legal gate rather than a preference.</t>
         </is>
       </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
-          <t>— nobody; this does not happen today</t>
+          <t>Clinician — obtains consent at the start-of-care visit</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>— no one today; this does not happen</t>
+          <t>— enforced by rule, not decided by anyone</t>
         </is>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>Does not exist today. Would derive from route and position.</t>
+          <t>HCHB, once signed at admission.</t>
         </is>
       </c>
       <c r="K82" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L82" s="20" t="inlineStr">
@@ -9301,39 +9731,44 @@
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>Per visit</t>
-        </is>
-      </c>
-      <c r="O82" s="22" t="inlineStr">
-        <is>
-          <t>Maybe</t>
+          <t>Per episode, signed at the start of care</t>
+        </is>
+      </c>
+      <c r="O82" s="21" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="P82" s="22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q82" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R82" s="18" t="inlineStr">
-        <is>
-          <t>Deterministic from position and route. Note it implies clinician location tracking, which is a conversation to have deliberately.</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q82" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R82" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S82" s="18" t="inlineStr">
         <is>
-          <t>Are we comfortable with the location tracking this implies, and have clinicians been consulted?</t>
+          <t>Added 19 Aug, and it puts a hard boundary on the automation the one-pager promises: consents are signed at the start-of-care visit, so no automated texting can precede admission and the readiness call before that first visit is necessarily a voice call.</t>
+        </is>
+      </c>
+      <c r="T82" s="18" t="inlineStr">
+        <is>
+          <t>Does this change what we can promise vendors about pre-admission outreach?</t>
         </is>
       </c>
     </row>
     <row r="83" ht="76" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>CO-05</t>
+          <t>CO-07</t>
         </is>
       </c>
       <c r="B83" s="25" t="inlineStr">
@@ -9341,10 +9776,14 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr"/>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t>Before the visit</t>
+          <t>When plans change</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr">
@@ -9354,79 +9793,84 @@
       </c>
       <c r="F83" s="18" t="inlineStr">
         <is>
-          <t>Channel and communication preferences</t>
+          <t>Rescheduling with the patient</t>
         </is>
       </c>
       <c r="G83" s="18" t="inlineStr">
         <is>
-          <t>How each patient wants to be reached — text, call or email — and what they have consented to. It decides whether any of the automation above actually lands.</t>
+          <t>Negotiating a new time when the planned one stops working. A system can propose slots; the negotiation itself is a conversation between people.</t>
         </is>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — captures it when it comes up</t>
+          <t>Clinician — for their own visits; Scheduler — when it comes back to the office</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinician or Scheduler, depending on who holds it</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>Phone numbers are in HCHB. Channel preference and consent are not systematically held.</t>
+          <t>The outcome lands in HCHB as a rescheduled visit; the negotiation is not recorded.</t>
         </is>
       </c>
       <c r="K83" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L83" s="20" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="M83" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinician / Scheduler</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>Per episode</t>
-        </is>
-      </c>
-      <c r="O83" s="22" t="inlineStr">
+          <t>On event</t>
+        </is>
+      </c>
+      <c r="O83" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P83" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P83" s="22" t="inlineStr">
+      <c r="Q83" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q83" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R83" s="18" t="inlineStr">
-        <is>
-          <t>Honour it, never assume it. Conflict risk: a vendor with its own communication model may not respect an existing preference store. Consent and opt-out rules also carry regulatory weight.</t>
+      <c r="R83" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S83" s="18" t="inlineStr">
         <is>
-          <t>Where would channel preference and consent live, and who captures it at admission?</t>
+          <t>Human negotiation around a moving constraint. Note that when rapid reschedule is switched on, a clinician moving their own visit inside the week creates no office work at all — so the volume the office sees is a branch configuration choice, not a fact.</t>
+        </is>
+      </c>
+      <c r="T83" s="18" t="inlineStr">
+        <is>
+          <t>Which branches have rapid reschedule enabled? It changes what the office actually sees.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="76" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>S-47</t>
+          <t>CO-08</t>
         </is>
       </c>
       <c r="B84" s="25" t="inlineStr">
@@ -9441,7 +9885,7 @@
       </c>
       <c r="D84" s="19" t="inlineStr">
         <is>
-          <t>Before the visit</t>
+          <t>When plans change</t>
         </is>
       </c>
       <c r="E84" s="18" t="inlineStr">
@@ -9451,79 +9895,84 @@
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
-          <t>Power of attorney and who can sign</t>
+          <t>Following up a failed or no-show visit</t>
         </is>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>Whether someone other than the patient holds legal authority to sign admission consents and to be the contact of record. Where a power of attorney exists the patient's own agreement does not satisfy consent, and some direct that the patient not be contacted at all.</t>
+          <t>Chasing the visit that did not happen — reaching the patient, rebooking, documenting. Left alone these become both a compliance problem and lost revenue.</t>
         </is>
       </c>
       <c r="H84" s="20" t="inlineStr">
         <is>
-          <t>Intake and Scheduler — capture it if it surfaces</t>
+          <t>Scheduler — follows up and rebooks</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — decides who to contact</t>
+          <t>Scheduler; DCS — when it will not resolve</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>Partly Commure at referral, otherwise manual. Not reliably known before the visit is booked.</t>
+          <t>HCHB — visit status and missed-visit workflow.</t>
         </is>
       </c>
       <c r="K84" s="21" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L84" s="20" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
+      <c r="M84" s="20" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>On event</t>
+        </is>
+      </c>
+      <c r="O84" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P84" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q84" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R84" s="21" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L84" s="20" t="inlineStr">
-        <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="M84" s="20" t="inlineStr">
-        <is>
-          <t>Scheduler — confirms who may be contacted</t>
-        </is>
-      </c>
-      <c r="N84" s="20" t="inlineStr">
-        <is>
-          <t>Per referral, before booking</t>
-        </is>
-      </c>
-      <c r="O84" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P84" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q84" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R84" s="18" t="inlineStr">
-        <is>
-          <t>Added 19 Aug. The failure it prevents is concrete: a nurse arrives for the start of care, the patient cannot sign, and the power of attorney is two states away. The visit is wasted and the clock keeps running.</t>
-        </is>
-      </c>
       <c r="S84" s="18" t="inlineStr">
         <is>
-          <t>Where would POA status be captured so the scheduler sees it before booking rather than after?</t>
+          <t>Detection is clean; the recovery pulls in every soft constraint again.</t>
+        </is>
+      </c>
+      <c r="T84" s="18" t="inlineStr">
+        <is>
+          <t>Nothing outstanding.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="76" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>CO-13</t>
+          <t>CO-09</t>
         </is>
       </c>
       <c r="B85" s="25" t="inlineStr">
@@ -9531,40 +9980,44 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr"/>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>Capacity, Scheduling</t>
+        </is>
+      </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t>Before the visit</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>When plans change</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
         <is>
-          <t>A verified number for the right person</t>
+          <t>Finding coverage when someone calls out</t>
         </is>
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>The confirmed phone number and reachable channel for the patient and, where it applies, the caregiver or power of attorney — including which of them is the right person to talk to about scheduling. Every piece of coordination depends on this, and today it is scattered.</t>
+          <t>The scramble when a clinician is out. It is owned jointly by the DCS and the scheduler, and it runs on who will actually say yes — calls, texts and Teams messages to full-time and per-diem staff, then reassignment or moving the visit to another day.</t>
         </is>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Intake and Scheduler — capture what they are given</t>
+          <t>DCS and Scheduler — jointly</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — works out who to call</t>
+          <t>DCS and Scheduler — jointly; DCS escalates for a start of care</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>Partly HCHB, partly Commure, partly neither. There is no single verified record.</t>
+          <t>No system holds this. It runs on phone, text and Teams, against the scheduler's knowledge of who might take it.</t>
         </is>
       </c>
       <c r="K85" s="21" t="inlineStr">
@@ -9574,49 +10027,54 @@
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>Automate</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="M85" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — owns the exception when nobody answers</t>
+          <t>DCS and Scheduler — jointly</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>Per referral, verified at admission</t>
-        </is>
-      </c>
-      <c r="O85" s="22" t="inlineStr">
+          <t>On event</t>
+        </is>
+      </c>
+      <c r="O85" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P85" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P85" s="22" t="inlineStr">
+      <c r="Q85" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q85" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R85" s="18" t="inlineStr">
-        <is>
-          <t>Added 19 Aug, and distinct from channel preference: a preference is no use without a working number for the right party. The failure it names is reminders going to a disconnected mobile while the daughter who books every visit is never contacted.</t>
+      <c r="R85" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="S85" s="18" t="inlineStr">
         <is>
-          <t>Who verifies the number, and at what point in admission?</t>
+          <t>Runs on the same relational willingness as the per-diem and elasticity rows. A system can assemble the candidate list and reach people directly; it cannot decide who will say yes. This is where an incentive on a hard-to-fill visit would attach.</t>
+        </is>
+      </c>
+      <c r="T85" s="18" t="inlineStr">
+        <is>
+          <t>Would we let the system contact clinicians directly with an open visit, or must a person always make the ask?</t>
         </is>
       </c>
     </row>
     <row r="86" ht="76" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>CO-14</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="B86" s="25" t="inlineStr">
@@ -9624,10 +10082,14 @@
           <t>Patient Engagement</t>
         </is>
       </c>
-      <c r="C86" s="18" t="inlineStr"/>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>Before the visit</t>
+          <t>When plans change</t>
         </is>
       </c>
       <c r="E86" s="18" t="inlineStr">
@@ -9637,79 +10099,84 @@
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
-          <t>Consent to contact, by channel</t>
+          <t>Incentives and offers on hard-to-fill visits</t>
         </is>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>Which channels we are legally allowed to use — texting, and sharing information with family — and whether the consent has actually been signed. A legal gate rather than a preference.</t>
+          <t>Surfacing a difficult visit to the clinicians who could take it, with whatever incentive or differential is attached. The one-pager now asks vendors about this and the questionnaire scores it — but no variable in the inventory covers it.</t>
         </is>
       </c>
       <c r="H86" s="20" t="inlineStr">
         <is>
-          <t>Clinician — obtains consent at the start-of-care visit</t>
+          <t>— does not exist today</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>— enforced by rule, not decided by anyone</t>
+          <t>— no one today; does not exist</t>
         </is>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
-          <t>HCHB, once signed at admission.</t>
+          <t>Nothing today. Pay model is in Workday; there is no mechanism for a visit-level offer.</t>
         </is>
       </c>
       <c r="K86" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
-          <t>Automate</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M86" s="20" t="inlineStr">
         <is>
-          <t>— exception only</t>
+          <t>Branch Leadership (ED) — would own the spend</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>Per episode, signed at the start of care</t>
-        </is>
-      </c>
-      <c r="O86" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>On event</t>
+        </is>
+      </c>
+      <c r="O86" s="21" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
         </is>
       </c>
       <c r="P86" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q86" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R86" s="18" t="inlineStr">
-        <is>
-          <t>Added 19 Aug, and it puts a hard boundary on the automation the one-pager promises: consents are signed at the start-of-care visit, so no automated texting can precede admission and the readiness call before that first visit is necessarily a voice call.</t>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="Q86" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R86" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="S86" s="18" t="inlineStr">
         <is>
-          <t>Does this change what we can promise vendors about pre-admission outreach?</t>
+          <t>A genuine gap, not an oversight: this was added to the vendor ask on 21 Aug and the 19 Aug inventory predates it. Recorded here so the workbook and the questionnaire stay aligned. Next free IDs after 19 Aug are SH-10, C-15, S-51 and CO-15.</t>
+        </is>
+      </c>
+      <c r="T86" s="18" t="inlineStr">
+        <is>
+          <t>Do we add this to the variable inventory as a new ID? It is currently asked of vendors but not modelled by us.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="76" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>CO-07</t>
+          <t>CO-10</t>
         </is>
       </c>
       <c r="B87" s="25" t="inlineStr">
@@ -9724,37 +10191,37 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
         <is>
-          <t>Rescheduling with the patient</t>
+          <t>Coordinating visits across disciplines</t>
         </is>
       </c>
       <c r="G87" s="18" t="inlineStr">
         <is>
-          <t>Negotiating a new time when the planned one stops working. A system can propose slots; the negotiation itself is a conversation between people.</t>
+          <t>Spacing the nurse, the therapist and the aide sensibly across a week rather than stacking two on one day and leaving the patient idle the next.</t>
         </is>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Clinician — for their own visits; Scheduler — when it comes back to the office</t>
+          <t>Scheduler — spaces them; Clinician — adjusts</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Clinician or Scheduler, depending on who holds it</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>The outcome lands in HCHB as a rescheduled visit; the negotiation is not recorded.</t>
+          <t>HCHB holds the visits; the spacing judgment is manual.</t>
         </is>
       </c>
       <c r="K87" s="21" t="inlineStr">
@@ -9764,49 +10231,54 @@
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="M87" s="20" t="inlineStr">
         <is>
-          <t>Clinician / Scheduler</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>On event</t>
-        </is>
-      </c>
-      <c r="O87" s="22" t="inlineStr">
+          <t>Weekly per patient</t>
+        </is>
+      </c>
+      <c r="O87" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
+        </is>
+      </c>
+      <c r="P87" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="P87" s="22" t="inlineStr">
+      <c r="Q87" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q87" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R87" s="18" t="inlineStr">
-        <is>
-          <t>Human negotiation around a moving constraint. Note that when rapid reschedule is switched on, a clinician moving their own visit inside the week creates no office work at all — so the volume the office sees is a branch configuration choice, not a fact.</t>
+      <c r="R87" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S87" s="18" t="inlineStr">
         <is>
-          <t>Which branches have rapid reschedule enabled? It changes what the office actually sees.</t>
+          <t>Rule-informed but bounded by what a patient will tolerate in a week. Propose, do not dictate.</t>
+        </is>
+      </c>
+      <c r="T87" s="18" t="inlineStr">
+        <is>
+          <t>Is there a standard on how many visits a patient should have in one day?</t>
         </is>
       </c>
     </row>
     <row r="88" ht="76" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>CO-08</t>
+          <t>CO-11</t>
         </is>
       </c>
       <c r="B88" s="25" t="inlineStr">
@@ -9821,37 +10293,37 @@
       </c>
       <c r="D88" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>Following up a failed or no-show visit</t>
+          <t>Keeping the team and the office in step</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
         <is>
-          <t>Chasing the visit that did not happen — reaching the patient, rebooking, documenting. Left alone these become both a compliance problem and lost revenue.</t>
+          <t>The connective work of telling the case manager and the office when something changes. Today it is the coordination-note habit — and how well it works depends entirely on people remembering.</t>
         </is>
       </c>
       <c r="H88" s="20" t="inlineStr">
         <is>
-          <t>Scheduler — follows up and rebooks</t>
+          <t>Scheduler and Clinician — write the notes</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Scheduler; DCS — when it will not resolve</t>
+          <t>Case Manager / Clinical Manager — act on what they read</t>
         </is>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
-          <t>HCHB — visit status and missed-visit workflow.</t>
+          <t>HCHB coordination notes.</t>
         </is>
       </c>
       <c r="K88" s="21" t="inlineStr">
@@ -9866,35 +10338,40 @@
       </c>
       <c r="M88" s="20" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Clinical Manager</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
-          <t>On event</t>
-        </is>
-      </c>
-      <c r="O88" s="22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="O88" s="21" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
         </is>
       </c>
       <c r="P88" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q88" s="21" t="inlineStr">
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q88" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R88" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R88" s="18" t="inlineStr">
-        <is>
-          <t>Detection is clean; the recovery pulls in every soft constraint again.</t>
-        </is>
-      </c>
       <c r="S88" s="18" t="inlineStr">
+        <is>
+          <t>Logging and notifying is automatable; deciding what deserves an escalation is human judgment.</t>
+        </is>
+      </c>
+      <c r="T88" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -9903,7 +10380,7 @@
     <row r="89" ht="76" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>CO-12</t>
         </is>
       </c>
       <c r="B89" s="25" t="inlineStr">
@@ -9913,92 +10390,97 @@
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Capacity, Scheduling</t>
         </is>
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
         <is>
-          <t>Incentives and offers on hard-to-fill visits</t>
+          <t>What coordination actually costs</t>
         </is>
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
-          <t>Surfacing a difficult visit to the clinicians who could take it, with whatever incentive or differential is attached. The one-pager now asks vendors about this and the questionnaire scores it — but no variable in the inventory covers it.</t>
+          <t>The time clinicians and schedulers spend on coordination rather than care. It is capacity, and today it is invisible — roughly forty-five minutes a day per clinician by one estimate, which is a visit.</t>
         </is>
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>— does not exist today</t>
+          <t>Everyone — it is spread across every role</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>— no one today; does not exist</t>
+          <t>— no one measures it today</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>Nothing today. Pay model is in Workday; there is no mechanism for a visit-level offer.</t>
+          <t>Not measured anywhere.</t>
         </is>
       </c>
       <c r="K89" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="M89" s="20" t="inlineStr">
         <is>
-          <t>Branch Leadership (ED) — would own the spend</t>
+          <t>Clinical Manager / Branch Leadership — to act on the trend</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>On event</t>
-        </is>
-      </c>
-      <c r="O89" s="22" t="inlineStr">
-        <is>
-          <t>--</t>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="O89" s="21" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
         </is>
       </c>
       <c r="P89" s="22" t="inlineStr">
         <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="Q89" s="22" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q89" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R89" s="18" t="inlineStr">
-        <is>
-          <t>A genuine gap, not an oversight: this was added to the vendor ask on 21 Aug and the 19 Aug inventory predates it. Recorded here so the workbook and the questionnaire stay aligned. Next free IDs after 19 Aug are SH-10, C-15, S-51 and CO-15.</t>
+      <c r="R89" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S89" s="18" t="inlineStr">
         <is>
-          <t>Do we add this to the variable inventory as a new ID? It is currently asked of vendors but not modelled by us.</t>
+          <t>Measure and surface it; do not try to control the people doing it. This is the number that turns the business case from theory into a figure the branch recognises.</t>
+        </is>
+      </c>
+      <c r="T89" s="18" t="inlineStr">
+        <is>
+          <t>Is there an appetite to measure this directly, or should it be estimated from the automation we remove?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S89"/>
+  <autoFilter ref="A1:T89"/>
   <conditionalFormatting sqref="J2:K89">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$K2="High"</formula>
@@ -10010,18 +10492,18 @@
       <formula>$K2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q89">
+  <conditionalFormatting sqref="R2:R89">
     <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
-      <formula>$Q2="High"</formula>
+      <formula>$R2="High"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="0">
-      <formula>$Q2="Medium"</formula>
+      <formula>$R2="Medium"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="0">
-      <formula>$Q2="Low"</formula>
+      <formula>$R2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="B2:B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$A$2:$A$4</formula1>
     </dataValidation>
@@ -10031,17 +10513,20 @@
     <dataValidation sqref="L2:L89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$G$2:$G$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$I$2:$I$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10054,7 +10539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10065,6 +10550,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10108,6 +10594,11 @@
           <t>Roles (for the two owner columns)</t>
         </is>
       </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
+          <t>Stays true on its own?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
@@ -10150,6 +10641,11 @@
           <t>Intake</t>
         </is>
       </c>
+      <c r="I2" s="27" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
@@ -10192,6 +10688,11 @@
           <t>Auth team</t>
         </is>
       </c>
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>Drifts — needs re-contact</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
@@ -10229,6 +10730,11 @@
           <t>Scheduler</t>
         </is>
       </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Live / computed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="C5" s="27" t="inlineStr">
@@ -10249,6 +10755,11 @@
       <c r="H5" s="27" t="inlineStr">
         <is>
           <t>DCS</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>This is the contact</t>
         </is>
       </c>
     </row>

--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Roles" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$T$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$U$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D73"/>
+  <dimension ref="B2:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1225,294 +1225,342 @@
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>High adoption sensitivity</t>
+          <t>...caught in the day-before round</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Rows where the change lands on clinicians. Design these with them.</t>
+          <t>The single recurring contact point the process already has. Today it is manual, every patient, every day.</t>
         </is>
       </c>
       <c r="D45" s="12">
-        <f>COUNTIF('Master List'!$R$2:$R$89,"High")</f>
+        <f>COUNTIF('Master List'!$P$2:$P$89,"Day before*")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Day-one must-haves</t>
+          <t>...caught in the weekly build</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MVP = Yes.</t>
+          <t>The clinician's own weekly planning pass.</t>
         </is>
       </c>
       <c r="D46" s="12">
-        <f>COUNTIF('Master List'!$P$2:$P$89,"Yes")</f>
+        <f>COUNTIF('Master List'!$P$2:$P$89,"Weekly*")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
+          <t>...with no re-check at all</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Drifts, and nothing catches it. Silent staleness.</t>
+        </is>
+      </c>
+      <c r="D47" s="12">
+        <f>COUNTIFS('Master List'!$O$2:$O$89,"Drifts*",'Master List'!$P$2:$P$89,"Not re-checked today")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>High adoption sensitivity</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Rows where the change lands on clinicians. Design these with them.</t>
+        </is>
+      </c>
+      <c r="D48" s="12">
+        <f>COUNTIF('Master List'!$S$2:$S$89,"High")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Day-one must-haves</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>MVP = Yes.</t>
+        </is>
+      </c>
+      <c r="D49" s="12">
+        <f>COUNTIF('Master List'!$Q$2:$Q$89,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
           <t>Knockout requirements</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Gating = Y. A product that cannot do these should not advance.</t>
         </is>
       </c>
-      <c r="D47" s="12">
-        <f>COUNTIF('Master List'!$Q$2:$Q$89,"Y")</f>
+      <c r="D50" s="12">
+        <f>COUNTIF('Master List'!$R$2:$R$89,"Y")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>A worked row, so the expected format is obvious</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Arena (8.19 workbook)</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>Capacity Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Also touches</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>Scheduling</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>One-pager group</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>Availability &amp; reach</t>
+          <t>C-03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Placement check</t>
+          <t>Arena (8.19 workbook)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>Aligned</t>
+          <t>Capacity Management</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>In plain terms</t>
+          <t>Also touches</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Which zip codes each clinician covers. Territories were drawn on thin data and have stayed static, so capacity drifts away from demand quietly.</t>
+          <t>Scheduling</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Who does the work today</t>
+          <t>One-pager group</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>DCS and Scheduler — assign and adjust</t>
+          <t>Availability &amp; reach</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Who reads it and decides today</t>
+          <t>Placement check</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>Branch Leadership (ED) with DCS — at the joint review when capacity tightens</t>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Where it lives today</t>
+          <t>In plain terms</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>HCHB holds the assignment where it has been entered; the working version is often the scheduler's own reference.</t>
+          <t>Which zip codes each clinician covers. Territories were drawn on thin data and have stayed static, so capacity drifts away from demand quietly.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Who does the work today</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>DCS and Scheduler — assign and adjust</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Future state</t>
+          <t>Who reads it and decides today</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>Assist — the tool proposes territory changes against a live census heat-map</t>
+          <t>Branch Leadership (ED) with DCS — at the joint review when capacity tightens</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Future state -- who decides</t>
+          <t>Where it lives today</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>Branch Leadership (ED) with DCS</t>
+          <t>HCHB holds the assignment where it has been entered; the working version is often the scheduler's own reference.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Trigger / how often</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>Quarterly, or on demand shift</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Adoption sensitivity</t>
+          <t>Future state</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Assist — the tool proposes territory changes against a live census heat-map</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Future state -- who decides</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Branch Leadership (ED) with DCS</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Editing conventions</t>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Trigger / how often</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Quarterly, or on demand shift</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Everything is editable</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Nothing is locked. The drop-down columns accept typed values too, so a shared answer like 'DCS and Scheduler' is always allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Say 'no one' when it is true</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>If nobody reads a report today, write '— no one today'. Those rows are counted above and they are where the value is.</t>
+          <t>Adoption sensitivity</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Keep IDs untouched</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>The ID column is the join key back to the 8.13 workbook. Never renumber it.</t>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Editing conventions</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
+          <t>Everything is editable</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Nothing is locked. The drop-down columns accept typed values too, so a shared answer like 'DCS and Scheduler' is always allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Say 'no one' when it is true</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>If nobody reads a report today, write '— no one today'. Those rows are counted above and they are where the value is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Keep IDs untouched</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>The ID column is the join key back to the 8.13 workbook. Never renumber it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
           <t>This does not overwrite the workbook</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>The 8.13 workbook stays authoritative for the variables themselves. This sheet adds the ownership and future-state layer on top.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="14" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Sources: variables and IDs from the 8.13 Compassus Capacity &amp; Scheduling Workbook (Variable Inventory + Definitions &amp; Concepts tabs). Plain-language wording follows the vendor one-pager as it stands in the 21 Aug questionnaire Overview tab. Current-state ownership follows the 17-18 Aug flow-mapping facts. Where-it-lives entries are first-pass hypotheses, not findings -- the confidence shading says how much to trust each one.</t>
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73"/>
+    <row r="75"/>
+    <row r="76"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B71:C73"/>
     <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B74:C76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T89"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1542,11 +1590,12 @@
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="62" customWidth="1" min="19" max="19"/>
-    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="62" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1627,25 +1676,30 @@
       </c>
       <c r="P1" s="15" t="inlineStr">
         <is>
+          <t>Re-checked when</t>
+        </is>
+      </c>
+      <c r="Q1" s="15" t="inlineStr">
+        <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="Q1" s="15" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>Gating</t>
         </is>
       </c>
-      <c r="R1" s="15" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>Adoption sensitivity</t>
         </is>
       </c>
-      <c r="S1" s="15" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>Why this posture / watch-out</t>
         </is>
       </c>
-      <c r="T1" s="15" t="inlineStr">
+      <c r="U1" s="15" t="inlineStr">
         <is>
           <t>Open question for the team</t>
         </is>
@@ -1727,27 +1781,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P2" s="22" t="inlineStr">
+      <c r="P2" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q2" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q2" s="22" t="inlineStr">
+      <c r="R2" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R2" s="21" t="inlineStr">
+      <c r="S2" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="T2" s="18" t="inlineStr">
         <is>
           <t>A clean roster fact in a system of record. The only risk is Workday and HCHB disagreeing.</t>
         </is>
       </c>
-      <c r="T2" s="18" t="inlineStr">
+      <c r="U2" s="18" t="inlineStr">
         <is>
           <t>Which system wins when Workday and HCHB disagree on who is active?</t>
         </is>
@@ -1829,27 +1888,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr">
+      <c r="P3" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R3" s="21" t="inlineStr">
+      <c r="S3" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S3" s="18" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
         <is>
           <t>Hard licensure fact, fully in the data.</t>
         </is>
       </c>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t>Are the discipline codes identical in Workday and HCHB, or do they need mapping?</t>
         </is>
@@ -1931,27 +1995,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="P4" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q4" s="22" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S4" s="18" t="inlineStr">
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t>Deterministic from discipline. The sensitivity is not the data, it is the change-management of moving work to assistants.</t>
         </is>
       </c>
-      <c r="T4" s="18" t="inlineStr">
+      <c r="U4" s="18" t="inlineStr">
         <is>
           <t>Is the assessing/assistant split written down as policy anywhere, or only understood?</t>
         </is>
@@ -2029,27 +2098,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="inlineStr">
+      <c r="R5" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R5" s="21" t="inlineStr">
+      <c r="S5" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S5" s="18" t="inlineStr">
+      <c r="T5" s="18" t="inlineStr">
         <is>
           <t>Clean employment attribute. Flagged as a conflict risk: a vendor that models FTE differently will fight the branch.</t>
         </is>
       </c>
-      <c r="T5" s="18" t="inlineStr">
+      <c r="U5" s="18" t="inlineStr">
         <is>
           <t>Do per-diem and contract clinicians carry an FTE value at all, or are they null?</t>
         </is>
@@ -2127,27 +2201,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="S6" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S6" s="18" t="inlineStr">
+      <c r="T6" s="18" t="inlineStr">
         <is>
           <t>A branch is only as capable as its thinnest discipline; this is the view that shows it.</t>
         </is>
       </c>
-      <c r="T6" s="18" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t>Who owns the branch roll-up today — is anyone producing this view at all?</t>
         </is>
@@ -2229,27 +2308,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q7" s="22" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R7" s="21" t="inlineStr">
+      <c r="S7" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr">
+      <c r="T7" s="18" t="inlineStr">
         <is>
           <t>The size of the buffer is legible; whether it actually flexes is relational. The system can show who is available, never assume they will say yes.</t>
         </is>
       </c>
-      <c r="T7" s="18" t="inlineStr">
+      <c r="U7" s="18" t="inlineStr">
         <is>
           <t>Is there a maintained per-diem availability list anywhere, or is it rebuilt from memory each time?</t>
         </is>
@@ -2331,27 +2415,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>Not re-checked today</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="inlineStr">
+      <c r="R8" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R8" s="21" t="inlineStr">
+      <c r="S8" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S8" s="18" t="inlineStr">
+      <c r="T8" s="18" t="inlineStr">
         <is>
           <t>Competency lives partly in reputation, not credentials. Surfacing it is useful; scoring it is not.</t>
         </is>
       </c>
-      <c r="T8" s="18" t="inlineStr">
+      <c r="U8" s="18" t="inlineStr">
         <is>
           <t>Is there a competency list per clinician anywhere today, and who would own keeping it current?</t>
         </is>
@@ -2429,27 +2518,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="R9" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R9" s="21" t="inlineStr">
+      <c r="S9" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S9" s="18" t="inlineStr">
+      <c r="T9" s="18" t="inlineStr">
         <is>
           <t>Headcount is clear; the true ramp curve is judgment. A system can propose a curve, a manager corrects it.</t>
         </is>
       </c>
-      <c r="T9" s="18" t="inlineStr">
+      <c r="U9" s="18" t="inlineStr">
         <is>
           <t>Is there a standard ramp expectation by discipline, or is it manager-by-manager?</t>
         </is>
@@ -2531,27 +2625,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P10" s="22" t="inlineStr">
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q10" s="22" t="inlineStr">
+      <c r="R10" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R10" s="21" t="inlineStr">
+      <c r="S10" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S10" s="18" t="inlineStr">
+      <c r="T10" s="18" t="inlineStr">
         <is>
           <t>Legible load once the rotation is recorded. The fairness question is human.</t>
         </is>
       </c>
-      <c r="T10" s="18" t="inlineStr">
+      <c r="U10" s="18" t="inlineStr">
         <is>
           <t>Is the rotation kept in HCHB, or on a separate branch calendar?</t>
         </is>
@@ -2633,27 +2732,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>On event — coverage and surge</t>
+        </is>
+      </c>
+      <c r="Q11" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q11" s="22" t="inlineStr">
+      <c r="R11" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R11" s="21" t="inlineStr">
+      <c r="S11" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="T11" s="18" t="inlineStr">
         <is>
           <t>A purely relational variable: the act of automating it changes what it measures. Surface who has said yes before; never auto-assign on it.</t>
         </is>
       </c>
-      <c r="T11" s="18" t="inlineStr">
+      <c r="U11" s="18" t="inlineStr">
         <is>
           <t>Would clinicians accept this being visible at all? This is a trust question before it is a data question.</t>
         </is>
@@ -2735,27 +2839,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P12" s="22" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>On event — coverage and surge</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="R12" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R12" s="21" t="inlineStr">
+      <c r="S12" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S12" s="18" t="inlineStr">
+      <c r="T12" s="18" t="inlineStr">
         <is>
           <t>Relational and pay-linked. This is the row that connects to the incentives idea in the one-pager: today there is no mechanism, only a phone call.</t>
         </is>
       </c>
-      <c r="T12" s="18" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t>If we attach an incentive to hard-to-fill visits, who sets it and who approves the spend?</t>
         </is>
@@ -2837,27 +2946,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q13" s="22" t="inlineStr">
+      <c r="R13" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R13" s="21" t="inlineStr">
+      <c r="S13" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="T13" s="18" t="inlineStr">
         <is>
           <t>A firm blackout once it is in the field. The integration being off is the single highest-value plumbing fix on this sheet — it makes every capacity number stale.</t>
         </is>
       </c>
-      <c r="T13" s="18" t="inlineStr">
+      <c r="U13" s="18" t="inlineStr">
         <is>
           <t>What would it take to turn the Workday-to-HCHB availability integration back on?</t>
         </is>
@@ -2939,27 +3053,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P14" s="22" t="inlineStr">
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="inlineStr">
+      <c r="R14" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R14" s="21" t="inlineStr">
+      <c r="S14" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S14" s="18" t="inlineStr">
+      <c r="T14" s="18" t="inlineStr">
         <is>
           <t>Territory lines look fixed but encode local knowledge and standing agreements. A tool should propose changes, never redraw them.</t>
         </is>
       </c>
-      <c r="T14" s="18" t="inlineStr">
+      <c r="U14" s="18" t="inlineStr">
         <is>
           <t>Is the current zip-to-clinician assignment complete in HCHB, or does the scheduler hold part of it?</t>
         </is>
@@ -3037,27 +3156,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="inlineStr">
+      <c r="R15" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R15" s="21" t="inlineStr">
+      <c r="S15" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="T15" s="18" t="inlineStr">
         <is>
           <t>Fixed boundary, cleanly held in configuration.</t>
         </is>
       </c>
-      <c r="T15" s="18" t="inlineStr">
+      <c r="U15" s="18" t="inlineStr">
         <is>
           <t>Does the recorded coverage area match what the branch actually accepts in practice?</t>
         </is>
@@ -3139,27 +3263,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P16" s="22" t="inlineStr">
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q16" s="22" t="inlineStr">
+      <c r="R16" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R16" s="21" t="inlineStr">
+      <c r="S16" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S16" s="18" t="inlineStr">
+      <c r="T16" s="18" t="inlineStr">
         <is>
           <t>Called out in the inventory as the initial variable in the whole equation. Pairing it with a live census heat-map is the highest-leverage capacity change identified.</t>
         </is>
       </c>
-      <c r="T16" s="18" t="inlineStr">
+      <c r="U16" s="18" t="inlineStr">
         <is>
           <t>How current is the zip assignment in HCHB right now — and when was it last reviewed against referral patterns?</t>
         </is>
@@ -3237,27 +3366,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="inlineStr">
+      <c r="R17" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R17" s="21" t="inlineStr">
+      <c r="S17" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S17" s="18" t="inlineStr">
+      <c r="T17" s="18" t="inlineStr">
         <is>
           <t>A modelling choice, not a live control. It reshapes both the capacity map and the routing at once, so it should be decided on purpose rather than inherited from a vendor default.</t>
         </is>
       </c>
-      <c r="T17" s="18" t="inlineStr">
+      <c r="U17" s="18" t="inlineStr">
         <is>
           <t>Do we want to make this call before vendor selection, or let the shortlist show us what is practical?</t>
         </is>
@@ -3339,27 +3473,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q18" s="22" t="inlineStr">
+      <c r="R18" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R18" s="21" t="inlineStr">
+      <c r="S18" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S18" s="18" t="inlineStr">
+      <c r="T18" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. The workbook's own example is the whole argument: one territory carrying about thirty patients across two full-time clinicians while the adjacent area declines starts. The tool proposes the misalignment; a person moves the boundary.</t>
         </is>
       </c>
-      <c r="T18" s="18" t="inlineStr">
+      <c r="U18" s="18" t="inlineStr">
         <is>
           <t>What cadence do we want for territory review, and who convenes it?</t>
         </is>
@@ -3441,27 +3580,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q19" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q19" s="22" t="inlineStr">
+      <c r="R19" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R19" s="21" t="inlineStr">
+      <c r="S19" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="T19" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and deliberately read-only. Inferring the preference from observed start times would record defeat as choice and then optimise to preserve it. Ask, record the answer, report the gap.</t>
         </is>
       </c>
-      <c r="T19" s="18" t="inlineStr">
+      <c r="U19" s="18" t="inlineStr">
         <is>
           <t>Who asks, and how often? This only works if the answer is collected rather than derived.</t>
         </is>
@@ -3543,27 +3687,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P20" s="22" t="inlineStr">
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q20" s="22" t="inlineStr">
+      <c r="R20" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R20" s="21" t="inlineStr">
+      <c r="S20" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S20" s="18" t="inlineStr">
+      <c r="T20" s="18" t="inlineStr">
         <is>
           <t>Derived and safe to compute. The catch is pending-auth visits, which are on no calendar and count toward nothing — so this number is already understated today.</t>
         </is>
       </c>
-      <c r="T20" s="18" t="inlineStr">
+      <c r="U20" s="18" t="inlineStr">
         <is>
           <t>Confirm which HCHB view the branch actually uses for committed points, and whether pending-auth visits appear anywhere in it.</t>
         </is>
@@ -3645,27 +3794,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P21" s="22" t="inlineStr">
+      <c r="P21" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q21" s="22" t="inlineStr">
+      <c r="R21" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R21" s="21" t="inlineStr">
+      <c r="S21" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S21" s="18" t="inlineStr">
+      <c r="T21" s="18" t="inlineStr">
         <is>
           <t>Pure derivation, but only as good as the point definitions underneath it. This is one of the clearest 'nobody can see this today' rows.</t>
         </is>
       </c>
-      <c r="T21" s="18" t="inlineStr">
+      <c r="U21" s="18" t="inlineStr">
         <is>
           <t>Does any current HCHB view show open points by day, or is this genuinely net-new?</t>
         </is>
@@ -3743,27 +3897,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P22" s="22" t="inlineStr">
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q22" s="22" t="inlineStr">
+      <c r="R22" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R22" s="21" t="inlineStr">
+      <c r="S22" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S22" s="18" t="inlineStr">
+      <c r="T22" s="18" t="inlineStr">
         <is>
           <t>The headline capacity number. Everything else on this sheet exists to make it trustworthy.</t>
         </is>
       </c>
-      <c r="T22" s="18" t="inlineStr">
+      <c r="U22" s="18" t="inlineStr">
         <is>
           <t>What is the decision this number should drive, and who makes it — ED, DCS, or intake?</t>
         </is>
@@ -3845,27 +4004,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q23" s="22" t="inlineStr">
+      <c r="R23" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R23" s="21" t="inlineStr">
+      <c r="S23" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S23" s="18" t="inlineStr">
+      <c r="T23" s="18" t="inlineStr">
         <is>
           <t>The growth-gating number. Distinct from total open room and more binding.</t>
         </is>
       </c>
-      <c r="T23" s="18" t="inlineStr">
+      <c r="U23" s="18" t="inlineStr">
         <is>
           <t>How does the branch decide today whether it can take another admission — what is the current proxy?</t>
         </is>
@@ -3947,27 +4111,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P24" s="22" t="inlineStr">
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q24" s="22" t="inlineStr">
+      <c r="R24" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R24" s="21" t="inlineStr">
+      <c r="S24" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S24" s="18" t="inlineStr">
+      <c r="T24" s="18" t="inlineStr">
         <is>
           <t>The values exist. What is undefined is how travel, documentation time and acuity are treated — and until that is settled, every derived capacity number inherits the ambiguity.</t>
         </is>
       </c>
-      <c r="T24" s="18" t="inlineStr">
+      <c r="U24" s="18" t="inlineStr">
         <is>
           <t>Open question #1: do points account for travel, documentation and acuity, or only visit type?</t>
         </is>
@@ -4045,27 +4214,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P25" s="22" t="inlineStr">
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q25" s="22" t="inlineStr">
+      <c r="R25" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R25" s="21" t="inlineStr">
+      <c r="S25" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S25" s="18" t="inlineStr">
+      <c r="T25" s="18" t="inlineStr">
         <is>
           <t>A policy constant and a simple lookup. Conflict risk: a vendor with its own opinion about targets will fight branch policy.</t>
         </is>
       </c>
-      <c r="T25" s="18" t="inlineStr">
+      <c r="U25" s="18" t="inlineStr">
         <is>
           <t>Are targets uniform across branches and disciplines, or do they vary?</t>
         </is>
@@ -4147,27 +4321,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P26" s="22" t="inlineStr">
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="inlineStr">
+      <c r="R26" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R26" s="21" t="inlineStr">
+      <c r="S26" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S26" s="18" t="inlineStr">
+      <c r="T26" s="18" t="inlineStr">
         <is>
           <t>Detecting the events is straightforward. What to do about the trend is the judgment, and it sits with the branch.</t>
         </is>
       </c>
-      <c r="T26" s="18" t="inlineStr">
+      <c r="U26" s="18" t="inlineStr">
         <is>
           <t>Is discharge date reliable enough in HCHB to forecast returning capacity?</t>
         </is>
@@ -4245,27 +4424,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P27" s="22" t="inlineStr">
+      <c r="P27" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Q27" s="22" t="inlineStr">
+      <c r="R27" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R27" s="21" t="inlineStr">
+      <c r="S27" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S27" s="18" t="inlineStr">
+      <c r="T27" s="18" t="inlineStr">
         <is>
           <t>Out of scope by choice, documented so the capacity math is transparent about what it holds constant.</t>
         </is>
       </c>
-      <c r="T27" s="18" t="inlineStr">
+      <c r="U27" s="18" t="inlineStr">
         <is>
           <t>Confirm this stays out of scope as the initiative moves into future-state design.</t>
         </is>
@@ -4347,27 +4531,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="P28" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R28" s="21" t="inlineStr">
+      <c r="S28" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S28" s="18" t="inlineStr">
+      <c r="T28" s="18" t="inlineStr">
         <is>
           <t>A set pattern with informal exceptions — the exceptions are the part no system holds.</t>
         </is>
       </c>
-      <c r="T28" s="18" t="inlineStr">
+      <c r="U28" s="18" t="inlineStr">
         <is>
           <t>Are working patterns recorded in HCHB per clinician, or reconstructed by the scheduler each week?</t>
         </is>
@@ -4445,27 +4634,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P29" s="22" t="inlineStr">
+      <c r="P29" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q29" s="22" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R29" s="21" t="inlineStr">
+      <c r="S29" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S29" s="18" t="inlineStr">
+      <c r="T29" s="18" t="inlineStr">
         <is>
           <t>Preferred and possible are two different things. Many clinicians want an early first visit and struggle to make it happen; it takes planning and patient motivation, not just a preference field.</t>
         </is>
       </c>
-      <c r="T29" s="18" t="inlineStr">
+      <c r="U29" s="18" t="inlineStr">
         <is>
           <t>Do we want to set a branch expectation on first-visit time, or keep it individual?</t>
         </is>
@@ -4543,27 +4737,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P30" s="22" t="inlineStr">
+      <c r="P30" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q30" s="22" t="inlineStr">
+      <c r="R30" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R30" s="21" t="inlineStr">
+      <c r="S30" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S30" s="18" t="inlineStr">
+      <c r="T30" s="18" t="inlineStr">
         <is>
           <t>Depends on a person's willingness. Assuming it is available damages the trust the whole thing runs on — surface only.</t>
         </is>
       </c>
-      <c r="T30" s="18" t="inlineStr">
+      <c r="U30" s="18" t="inlineStr">
         <is>
           <t>None — this row is intentionally read-only.</t>
         </is>
@@ -4641,27 +4840,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P31" s="22" t="inlineStr">
+      <c r="P31" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q31" s="22" t="inlineStr">
+      <c r="R31" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R31" s="21" t="inlineStr">
+      <c r="S31" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S31" s="18" t="inlineStr">
+      <c r="T31" s="18" t="inlineStr">
         <is>
           <t>A capturable personal habit. Worth knowing, not worth enforcing.</t>
         </is>
       </c>
-      <c r="T31" s="18" t="inlineStr">
+      <c r="U31" s="18" t="inlineStr">
         <is>
           <t>Would clinicians be willing to record this, or does it feel like surveillance?</t>
         </is>
@@ -4739,27 +4943,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P32" s="22" t="inlineStr">
+      <c r="P32" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q32" s="22" t="inlineStr">
+      <c r="R32" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R32" s="21" t="inlineStr">
+      <c r="S32" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S32" s="18" t="inlineStr">
+      <c r="T32" s="18" t="inlineStr">
         <is>
           <t>Same shape as the lunch pattern. Note that documentation time is real capacity consumed, and today it is invisible in the point math.</t>
         </is>
       </c>
-      <c r="T32" s="18" t="inlineStr">
+      <c r="U32" s="18" t="inlineStr">
         <is>
           <t>Should documentation time be represented in the point system? Ties to open question #1.</t>
         </is>
@@ -4837,27 +5046,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P33" s="22" t="inlineStr">
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q33" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q33" s="22" t="inlineStr">
+      <c r="R33" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R33" s="21" t="inlineStr">
+      <c r="S33" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S33" s="18" t="inlineStr">
+      <c r="T33" s="18" t="inlineStr">
         <is>
           <t>A personal daily rhythm that varies. Hard to predict reliably and easily disrupted by a system that assumes it knows — read only.</t>
         </is>
       </c>
-      <c r="T33" s="18" t="inlineStr">
+      <c r="U33" s="18" t="inlineStr">
         <is>
           <t>None — intentionally read-only.</t>
         </is>
@@ -4935,27 +5149,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P34" s="22" t="inlineStr">
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q34" s="22" t="inlineStr">
+      <c r="R34" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R34" s="21" t="inlineStr">
+      <c r="S34" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S34" s="18" t="inlineStr">
+      <c r="T34" s="18" t="inlineStr">
         <is>
           <t>A firm edge once known. The knowing is the tacit part.</t>
         </is>
       </c>
-      <c r="T34" s="18" t="inlineStr">
+      <c r="U34" s="18" t="inlineStr">
         <is>
           <t>Is there a place a clinician could record a standing hard stop today?</t>
         </is>
@@ -5033,27 +5252,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P35" s="22" t="inlineStr">
+      <c r="P35" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q35" s="22" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R35" s="21" t="inlineStr">
+      <c r="S35" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S35" s="18" t="inlineStr">
+      <c r="T35" s="18" t="inlineStr">
         <is>
           <t>A personal ceiling, capturable and worth confirming. Conflict risk: a vendor that packs to points alone will breach it.</t>
         </is>
       </c>
-      <c r="T35" s="18" t="inlineStr">
+      <c r="U35" s="18" t="inlineStr">
         <is>
           <t>Do we want a branch-level maximum as well as an individual one?</t>
         </is>
@@ -5135,27 +5359,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P36" s="22" t="inlineStr">
+      <c r="P36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="R36" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R36" s="21" t="inlineStr">
+      <c r="S36" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S36" s="18" t="inlineStr">
+      <c r="T36" s="18" t="inlineStr">
         <is>
           <t>A legible anchor once captured. Using home addresses for routing has a privacy dimension worth settling early.</t>
         </is>
       </c>
-      <c r="T36" s="18" t="inlineStr">
+      <c r="U36" s="18" t="inlineStr">
         <is>
           <t>Can we use clinician home addresses for drive-time calculation, and has that been agreed with them?</t>
         </is>
@@ -5233,27 +5462,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P37" s="22" t="inlineStr">
+      <c r="P37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q37" s="22" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R37" s="21" t="inlineStr">
+      <c r="S37" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S37" s="18" t="inlineStr">
+      <c r="T37" s="18" t="inlineStr">
         <is>
           <t>Clear in HCHB. Note that each discipline plots to clinical need without seeing payer limits at that moment — which is where the auth collision starts.</t>
         </is>
       </c>
-      <c r="T37" s="18" t="inlineStr">
+      <c r="U37" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding — this row is solid.</t>
         </is>
@@ -5331,27 +5565,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P38" s="22" t="inlineStr">
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q38" s="22" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R38" s="21" t="inlineStr">
+      <c r="S38" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S38" s="18" t="inlineStr">
+      <c r="T38" s="18" t="inlineStr">
         <is>
           <t>Clean order attribute.</t>
         </is>
       </c>
-      <c r="T38" s="18" t="inlineStr">
+      <c r="U38" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5433,27 +5672,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P39" s="22" t="inlineStr">
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q39" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q39" s="22" t="inlineStr">
+      <c r="R39" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R39" s="21" t="inlineStr">
+      <c r="S39" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S39" s="18" t="inlineStr">
+      <c r="T39" s="18" t="inlineStr">
         <is>
           <t>The largest single bottleneck in current-state scheduling, and the most tractable: the rules already exist in writing before they are needed. Surfacing the coordination note at plan-of-care creation is the highest-value, lowest-complexity win identified. Pending-auth visits sit on no calendar and count toward nothing — if you cannot see it, you cannot plan it.</t>
         </is>
       </c>
-      <c r="T39" s="18" t="inlineStr">
+      <c r="U39" s="18" t="inlineStr">
         <is>
           <t>Can the auth coordination note be surfaced into the plan-of-care screen, and who owns that change?</t>
         </is>
@@ -5535,27 +5779,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P40" s="22" t="inlineStr">
+      <c r="P40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q40" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q40" s="22" t="inlineStr">
+      <c r="R40" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R40" s="21" t="inlineStr">
+      <c r="S40" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S40" s="18" t="inlineStr">
+      <c r="T40" s="18" t="inlineStr">
         <is>
           <t>Flagged in the inventory as a bottleneck awaiting DCS workflow. It affects how capacity looks as well as what gets scheduled.</t>
         </is>
       </c>
-      <c r="T40" s="18" t="inlineStr">
+      <c r="U40" s="18" t="inlineStr">
         <is>
           <t>What is the current DCS add-on workflow, and is it consistent across branches?</t>
         </is>
@@ -5633,27 +5882,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P41" s="22" t="inlineStr">
+      <c r="P41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q41" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q41" s="22" t="inlineStr">
+      <c r="R41" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R41" s="21" t="inlineStr">
+      <c r="S41" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S41" s="18" t="inlineStr">
+      <c r="T41" s="18" t="inlineStr">
         <is>
           <t>A hard, legible clock — among the safest things to enforce automatically.</t>
         </is>
       </c>
-      <c r="T41" s="18" t="inlineStr">
+      <c r="U41" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5735,27 +5989,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P42" s="22" t="inlineStr">
+      <c r="P42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q42" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q42" s="22" t="inlineStr">
+      <c r="R42" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R42" s="21" t="inlineStr">
+      <c r="S42" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S42" s="18" t="inlineStr">
+      <c r="T42" s="18" t="inlineStr">
         <is>
           <t>A hard regulatory clock, fully clear — described in the inventory as the safest automation win available.</t>
         </is>
       </c>
-      <c r="T42" s="18" t="inlineStr">
+      <c r="U42" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5833,27 +6092,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P43" s="22" t="inlineStr">
+      <c r="P43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q43" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q43" s="22" t="inlineStr">
+      <c r="R43" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R43" s="21" t="inlineStr">
+      <c r="S43" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S43" s="18" t="inlineStr">
+      <c r="T43" s="18" t="inlineStr">
         <is>
           <t>Regulatory window; enforce and flag. Recert visits are already on the calendar from the original plan of care.</t>
         </is>
       </c>
-      <c r="T43" s="18" t="inlineStr">
+      <c r="U43" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -5935,27 +6199,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P44" s="22" t="inlineStr">
+      <c r="P44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q44" s="22" t="inlineStr">
+      <c r="R44" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R44" s="21" t="inlineStr">
+      <c r="S44" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S44" s="18" t="inlineStr">
+      <c r="T44" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. Queue depth and age are countable, but the queue is other people's work — surface it in front of the people it blocks, do not reorder it.</t>
         </is>
       </c>
-      <c r="T44" s="18" t="inlineStr">
+      <c r="U44" s="18" t="inlineStr">
         <is>
           <t>Can queue age be reported daily, and who owns acting on it?</t>
         </is>
@@ -6033,27 +6302,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P45" s="22" t="inlineStr">
+      <c r="P45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q45" s="22" t="inlineStr">
+      <c r="R45" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R45" s="21" t="inlineStr">
+      <c r="S45" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S45" s="18" t="inlineStr">
+      <c r="T45" s="18" t="inlineStr">
         <is>
           <t>A hard gate and fully legible. The sensitivity is the flip side: auto-assigning routine visits to assistants opens a lot of capacity but is a significant change-management conversation.</t>
         </is>
       </c>
-      <c r="T45" s="18" t="inlineStr">
+      <c r="U45" s="18" t="inlineStr">
         <is>
           <t>How far do we want to push routine visits to assistants, and who owns that decision?</t>
         </is>
@@ -6135,27 +6409,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P46" s="22" t="inlineStr">
+      <c r="P46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q46" s="22" t="inlineStr">
+      <c r="R46" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R46" s="21" t="inlineStr">
+      <c r="S46" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S46" s="18" t="inlineStr">
+      <c r="T46" s="18" t="inlineStr">
         <is>
           <t>Only as good as the competency data, which is incomplete today. This is human work performed on information the system does not hold.</t>
         </is>
       </c>
-      <c r="T46" s="18" t="inlineStr">
+      <c r="U46" s="18" t="inlineStr">
         <is>
           <t>Would we build a competency register, and who maintains it?</t>
         </is>
@@ -6233,27 +6512,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P47" s="22" t="inlineStr">
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>At recertification</t>
+        </is>
+      </c>
+      <c r="Q47" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q47" s="22" t="inlineStr">
+      <c r="R47" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R47" s="21" t="inlineStr">
+      <c r="S47" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S47" s="18" t="inlineStr">
+      <c r="T47" s="18" t="inlineStr">
         <is>
           <t>Clinical judgment with patient-safety consequences. Recommend, never decide. Useful for triage when coverage is short.</t>
         </is>
       </c>
-      <c r="T47" s="18" t="inlineStr">
+      <c r="U47" s="18" t="inlineStr">
         <is>
           <t>Do we have any usable acuity measure today, or is it entirely judgment?</t>
         </is>
@@ -6331,27 +6615,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P48" s="22" t="inlineStr">
+      <c r="P48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q48" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q48" s="22" t="inlineStr">
+      <c r="R48" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R48" s="21" t="inlineStr">
+      <c r="S48" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S48" s="18" t="inlineStr">
+      <c r="T48" s="18" t="inlineStr">
         <is>
           <t>A documented hard gate the system should simply honour — but only once it is actually written down somewhere the system can read.</t>
         </is>
       </c>
-      <c r="T48" s="18" t="inlineStr">
+      <c r="U48" s="18" t="inlineStr">
         <is>
           <t>Where are clinician restrictions recorded today? This may be the easiest structured-data win on the sheet.</t>
         </is>
@@ -6433,27 +6722,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P49" s="22" t="inlineStr">
+      <c r="P49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q49" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q49" s="22" t="inlineStr">
+      <c r="R49" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R49" s="21" t="inlineStr">
+      <c r="S49" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S49" s="18" t="inlineStr">
+      <c r="T49" s="18" t="inlineStr">
         <is>
           <t>Load-bearing but invisible. Protect it explicitly rather than scoring it against efficiency.</t>
         </is>
       </c>
-      <c r="T49" s="18" t="inlineStr">
+      <c r="U49" s="18" t="inlineStr">
         <is>
           <t>How much continuity are we willing to trade for routing efficiency? A policy call, not a technical one.</t>
         </is>
@@ -6531,27 +6825,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P50" s="22" t="inlineStr">
+      <c r="P50" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q50" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q50" s="22" t="inlineStr">
+      <c r="R50" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R50" s="21" t="inlineStr">
+      <c r="S50" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S50" s="18" t="inlineStr">
+      <c r="T50" s="18" t="inlineStr">
         <is>
           <t>Rule-based and legible.</t>
         </is>
       </c>
-      <c r="T50" s="18" t="inlineStr">
+      <c r="U50" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -6629,27 +6928,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P51" s="22" t="inlineStr">
+      <c r="P51" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q51" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q51" s="22" t="inlineStr">
+      <c r="R51" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R51" s="21" t="inlineStr">
+      <c r="S51" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S51" s="18" t="inlineStr">
+      <c r="T51" s="18" t="inlineStr">
         <is>
           <t>Clinical judgment with patient-safety consequences — flag it, never decide it. Also the clearest place where a rehospitalisation-risk signal would earn its keep.</t>
         </is>
       </c>
-      <c r="T51" s="18" t="inlineStr">
+      <c r="U51" s="18" t="inlineStr">
         <is>
           <t>Could clinically driven timing be flagged distinctly from preference in the record?</t>
         </is>
@@ -6727,27 +7031,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P52" s="22" t="inlineStr">
+      <c r="P52" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q52" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q52" s="22" t="inlineStr">
+      <c r="R52" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R52" s="21" t="inlineStr">
+      <c r="S52" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S52" s="18" t="inlineStr">
+      <c r="T52" s="18" t="inlineStr">
         <is>
           <t>Partly rule, partly judgment. A system can propose the sequence and flag conflicts; the clinician confirms.</t>
         </is>
       </c>
-      <c r="T52" s="18" t="inlineStr">
+      <c r="U52" s="18" t="inlineStr">
         <is>
           <t>Are there written sequencing rules, or is this entirely clinician knowledge?</t>
         </is>
@@ -6825,27 +7134,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P53" s="22" t="inlineStr">
+      <c r="P53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q53" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q53" s="22" t="inlineStr">
+      <c r="R53" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R53" s="21" t="inlineStr">
+      <c r="S53" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S53" s="18" t="inlineStr">
+      <c r="T53" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. A risk score may inform priority; it may not silently reorder a clinician's day or override clinical judgment. The natural companion to acuity matching when coverage is short.</t>
         </is>
       </c>
-      <c r="T53" s="18" t="inlineStr">
+      <c r="U53" s="18" t="inlineStr">
         <is>
           <t>Is Pulse data reachable from scheduling today, and in what form?</t>
         </is>
@@ -6927,27 +7241,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P54" s="22" t="inlineStr">
+      <c r="P54" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q54" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q54" s="22" t="inlineStr">
+      <c r="R54" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R54" s="21" t="inlineStr">
+      <c r="S54" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S54" s="18" t="inlineStr">
+      <c r="T54" s="18" t="inlineStr">
         <is>
           <t>Geometry, and safely reversible. The efficiency gain here is real rather than borrowed from someone's slack.</t>
         </is>
       </c>
-      <c r="T54" s="18" t="inlineStr">
+      <c r="U54" s="18" t="inlineStr">
         <is>
           <t>What routing data does HCHB actually use today — distance, or real drive time?</t>
         </is>
@@ -7029,27 +7348,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P55" s="22" t="inlineStr">
+      <c r="P55" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q55" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q55" s="22" t="inlineStr">
+      <c r="R55" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R55" s="21" t="inlineStr">
+      <c r="S55" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S55" s="18" t="inlineStr">
+      <c r="T55" s="18" t="inlineStr">
         <is>
           <t>Deterministic routing maths.</t>
         </is>
       </c>
-      <c r="T55" s="18" t="inlineStr">
+      <c r="U55" s="18" t="inlineStr">
         <is>
           <t>Is mileage currently reported anywhere the branch actually looks at?</t>
         </is>
@@ -7127,27 +7451,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P56" s="22" t="inlineStr">
+      <c r="P56" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q56" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q56" s="22" t="inlineStr">
+      <c r="R56" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R56" s="21" t="inlineStr">
+      <c r="S56" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S56" s="18" t="inlineStr">
+      <c r="T56" s="18" t="inlineStr">
         <is>
           <t>A legible skeleton pinned by tacit anchors. Propose the sequence; let the person place the anchors.</t>
         </is>
       </c>
-      <c r="T56" s="18" t="inlineStr">
+      <c r="U56" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -7229,27 +7558,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P57" s="22" t="inlineStr">
+      <c r="P57" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q57" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q57" s="22" t="inlineStr">
+      <c r="R57" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R57" s="21" t="inlineStr">
+      <c r="S57" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S57" s="18" t="inlineStr">
+      <c r="T57" s="18" t="inlineStr">
         <is>
           <t>Enforceable once captured; capture is the weak point. Standardising this would move patient satisfaction and team efficiency together — and it is a visible change for clinicians.</t>
         </is>
       </c>
-      <c r="T57" s="18" t="inlineStr">
+      <c r="U57" s="18" t="inlineStr">
         <is>
           <t>Do we want to move to committed time windows, and what would that cost in flexibility?</t>
         </is>
@@ -7327,27 +7661,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P58" s="22" t="inlineStr">
+      <c r="P58" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q58" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q58" s="22" t="inlineStr">
+      <c r="R58" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R58" s="21" t="inlineStr">
+      <c r="S58" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S58" s="18" t="inlineStr">
+      <c r="T58" s="18" t="inlineStr">
         <is>
           <t>Numbered S-45 on 19 Aug. Where it applies the slot is removed from the route rather than flagged for override. Currently invisible to any scheduling logic, and it varies by market.</t>
         </is>
       </c>
-      <c r="T58" s="18" t="inlineStr">
+      <c r="U58" s="18" t="inlineStr">
         <is>
           <t>Which markets have safety rules today, and where are they written down?</t>
         </is>
@@ -7429,27 +7768,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P59" s="22" t="inlineStr">
+      <c r="P59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q59" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q59" s="22" t="inlineStr">
+      <c r="R59" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R59" s="21" t="inlineStr">
+      <c r="S59" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S59" s="18" t="inlineStr">
+      <c r="T59" s="18" t="inlineStr">
         <is>
           <t>A target, not a law. Forcing it flattens the clinician's own rhythm, which costs more than it saves.</t>
         </is>
       </c>
-      <c r="T59" s="18" t="inlineStr">
+      <c r="U59" s="18" t="inlineStr">
         <is>
           <t>Is 42% by Tuesday the standard we want to hold branches to?</t>
         </is>
@@ -7531,27 +7875,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P60" s="22" t="inlineStr">
+      <c r="P60" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q60" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q60" s="22" t="inlineStr">
+      <c r="R60" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R60" s="21" t="inlineStr">
+      <c r="S60" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S60" s="18" t="inlineStr">
+      <c r="T60" s="18" t="inlineStr">
         <is>
           <t>A derived read, safe to surface. This is the archetype of the pattern you described: the system can produce it, but somebody has to look and act.</t>
         </is>
       </c>
-      <c r="T60" s="18" t="inlineStr">
+      <c r="U60" s="18" t="inlineStr">
         <is>
           <t>Who should own the daily pace read — Clinical Manager, Scheduler, or both?</t>
         </is>
@@ -7633,27 +7982,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P61" s="22" t="inlineStr">
+      <c r="P61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q61" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q61" s="22" t="inlineStr">
+      <c r="R61" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R61" s="21" t="inlineStr">
+      <c r="S61" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S61" s="18" t="inlineStr">
+      <c r="T61" s="18" t="inlineStr">
         <is>
           <t>Optimisable, but it touches human routines — assist rather than dictate.</t>
         </is>
       </c>
-      <c r="T61" s="18" t="inlineStr">
+      <c r="U61" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -7735,27 +8089,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P62" s="22" t="inlineStr">
+      <c r="P62" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q62" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q62" s="22" t="inlineStr">
+      <c r="R62" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R62" s="21" t="inlineStr">
+      <c r="S62" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S62" s="18" t="inlineStr">
+      <c r="T62" s="18" t="inlineStr">
         <is>
           <t>Sensing the miss is legible; the recovery pulls the whole problem back in. Note the visit states run scheduled, then documentation pending, then missed — so 'missed' is a late signal.</t>
         </is>
       </c>
-      <c r="T62" s="18" t="inlineStr">
+      <c r="U62" s="18" t="inlineStr">
         <is>
           <t>Can we detect a likely miss earlier than the missed status appears?</t>
         </is>
@@ -7833,27 +8192,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P63" s="22" t="inlineStr">
+      <c r="P63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q63" s="22" t="inlineStr">
+      <c r="R63" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R63" s="21" t="inlineStr">
+      <c r="S63" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S63" s="18" t="inlineStr">
+      <c r="T63" s="18" t="inlineStr">
         <is>
           <t>Workflow and compliance prompting — safe to automate, and already partly automated.</t>
         </is>
       </c>
-      <c r="T63" s="18" t="inlineStr">
+      <c r="U63" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -7935,27 +8299,32 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P64" s="22" t="inlineStr">
+      <c r="P64" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q64" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q64" s="22" t="inlineStr">
+      <c r="R64" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R64" s="21" t="inlineStr">
+      <c r="S64" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S64" s="18" t="inlineStr">
+      <c r="T64" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and it constrains the whole design: nothing may depend on real-time visit state read out of HCHB. The workbook's example is stark — a clinician who called an ambulance has started a visit that did not happen, and the schedule still reads as worked.</t>
         </is>
       </c>
-      <c r="T64" s="18" t="inlineStr">
+      <c r="U64" s="18" t="inlineStr">
         <is>
           <t>How long is the blind window in practice? Nobody has measured it.</t>
         </is>
@@ -8037,27 +8406,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P65" s="22" t="inlineStr">
+      <c r="P65" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q65" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q65" s="22" t="inlineStr">
+      <c r="R65" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R65" s="21" t="inlineStr">
+      <c r="S65" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S65" s="18" t="inlineStr">
+      <c r="T65" s="18" t="inlineStr">
         <is>
           <t>Hard once captured, but a stale refusal causes a failed visit — and in practice these soften with relationship. Worth re-testing rather than treating as permanent.</t>
         </is>
       </c>
-      <c r="T65" s="18" t="inlineStr">
+      <c r="U65" s="18" t="inlineStr">
         <is>
           <t>Should refusals carry a review date so they do not calcify?</t>
         </is>
@@ -8139,27 +8513,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P66" s="22" t="inlineStr">
+      <c r="P66" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q66" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q66" s="22" t="inlineStr">
+      <c r="R66" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R66" s="21" t="inlineStr">
+      <c r="S66" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S66" s="18" t="inlineStr">
+      <c r="T66" s="18" t="inlineStr">
         <is>
           <t>Optimise toward it, confirm before committing.</t>
         </is>
       </c>
-      <c r="T66" s="18" t="inlineStr">
+      <c r="U66" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -8237,27 +8616,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P67" s="22" t="inlineStr">
+      <c r="P67" s="20" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
+      <c r="Q67" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q67" s="22" t="inlineStr">
+      <c r="R67" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R67" s="21" t="inlineStr">
+      <c r="S67" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S67" s="18" t="inlineStr">
+      <c r="T67" s="18" t="inlineStr">
         <is>
           <t>A standing constraint, but patient-reported — trust and verify.</t>
         </is>
       </c>
-      <c r="T67" s="18" t="inlineStr">
+      <c r="U67" s="18" t="inlineStr">
         <is>
           <t>Could standing commitments be captured as structured dates rather than free text?</t>
         </is>
@@ -8339,27 +8723,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P68" s="22" t="inlineStr">
+      <c r="P68" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q68" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q68" s="22" t="inlineStr">
+      <c r="R68" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R68" s="21" t="inlineStr">
+      <c r="S68" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S68" s="18" t="inlineStr">
+      <c r="T68" s="18" t="inlineStr">
         <is>
           <t>The clearest 'surface, never decide' row on the sheet: a hard rule, a changing informal input, and a patient-safety consequence if it is wrong.</t>
         </is>
       </c>
-      <c r="T68" s="18" t="inlineStr">
+      <c r="U68" s="18" t="inlineStr">
         <is>
           <t>How often does caregiver availability change mid-episode, and does anyone update the note when it does?</t>
         </is>
@@ -8441,27 +8830,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P69" s="22" t="inlineStr">
+      <c r="P69" s="20" t="inlineStr">
+        <is>
+          <t>At start of care</t>
+        </is>
+      </c>
+      <c r="Q69" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q69" s="22" t="inlineStr">
+      <c r="R69" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R69" s="21" t="inlineStr">
+      <c r="S69" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S69" s="18" t="inlineStr">
+      <c r="T69" s="18" t="inlineStr">
         <is>
           <t>Cognition plus caregiver dependency plus safety. Automation must only surface.</t>
         </is>
       </c>
-      <c r="T69" s="18" t="inlineStr">
+      <c r="U69" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding — but confirm the note reliably reaches the scheduler.</t>
         </is>
@@ -8543,27 +8937,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P70" s="22" t="inlineStr">
+      <c r="P70" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q70" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q70" s="22" t="inlineStr">
+      <c r="R70" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R70" s="21" t="inlineStr">
+      <c r="S70" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S70" s="18" t="inlineStr">
+      <c r="T70" s="18" t="inlineStr">
         <is>
           <t>Two undocumented moving calendars. A system can show what it last heard; it cannot know.</t>
         </is>
       </c>
-      <c r="T70" s="18" t="inlineStr">
+      <c r="U70" s="18" t="inlineStr">
         <is>
           <t>Is there any value in capturing caregiver availability as structured data, or is it too volatile to be worth it?</t>
         </is>
@@ -8645,27 +9044,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P71" s="22" t="inlineStr">
+      <c r="P71" s="20" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
+      <c r="Q71" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q71" s="22" t="inlineStr">
+      <c r="R71" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R71" s="21" t="inlineStr">
+      <c r="S71" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S71" s="18" t="inlineStr">
+      <c r="T71" s="18" t="inlineStr">
         <is>
           <t>Capturable if reported. The failure mode is a visit booked into an appointment nobody knew about.</t>
         </is>
       </c>
-      <c r="T71" s="18" t="inlineStr">
+      <c r="U71" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -8743,27 +9147,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P72" s="22" t="inlineStr">
+      <c r="P72" s="20" t="inlineStr">
+        <is>
+          <t>At start of care</t>
+        </is>
+      </c>
+      <c r="Q72" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Q72" s="22" t="inlineStr">
+      <c r="R72" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R72" s="21" t="inlineStr">
+      <c r="S72" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S72" s="18" t="inlineStr">
+      <c r="T72" s="18" t="inlineStr">
         <is>
           <t>Sensitive. Surface and confirm rather than auto-matching on it.</t>
         </is>
       </c>
-      <c r="T72" s="18" t="inlineStr">
+      <c r="U72" s="18" t="inlineStr">
         <is>
           <t>Is there a policy on how this is recorded and honoured?</t>
         </is>
@@ -8845,27 +9254,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P73" s="22" t="inlineStr">
+      <c r="P73" s="20" t="inlineStr">
+        <is>
+          <t>At start of care</t>
+        </is>
+      </c>
+      <c r="Q73" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q73" s="22" t="inlineStr">
+      <c r="R73" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R73" s="21" t="inlineStr">
+      <c r="S73" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S73" s="18" t="inlineStr">
+      <c r="T73" s="18" t="inlineStr">
         <is>
           <t>Capturable on both sides, and worth confirming specifically for teaching-critical visits.</t>
         </is>
       </c>
-      <c r="T73" s="18" t="inlineStr">
+      <c r="U73" s="18" t="inlineStr">
         <is>
           <t>Do we hold clinician language capability anywhere today?</t>
         </is>
@@ -8943,27 +9357,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P74" s="22" t="inlineStr">
+      <c r="P74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q74" s="22" t="inlineStr">
+      <c r="R74" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R74" s="21" t="inlineStr">
+      <c r="S74" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S74" s="18" t="inlineStr">
+      <c r="T74" s="18" t="inlineStr">
         <is>
           <t>Automate the trigger and the routine parts; keep a person on the line for the judgment. This is the highest-value human call in the admission chain.</t>
         </is>
       </c>
-      <c r="T74" s="18" t="inlineStr">
+      <c r="U74" s="18" t="inlineStr">
         <is>
           <t>If outreach is automated, how do we preserve the 'is the patient really home' check?</t>
         </is>
@@ -9045,27 +9464,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P75" s="22" t="inlineStr">
+      <c r="P75" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q75" s="22" t="inlineStr">
+      <c r="R75" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R75" s="21" t="inlineStr">
+      <c r="S75" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S75" s="18" t="inlineStr">
+      <c r="T75" s="18" t="inlineStr">
         <is>
           <t>Feeds directly off the caregiver-availability rows, which are the least reliable data on the sheet. Surface what is known; do not presume it is current.</t>
         </is>
       </c>
-      <c r="T75" s="18" t="inlineStr">
+      <c r="U75" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding — but this row depends on S-28 and S-30 being right.</t>
         </is>
@@ -9147,27 +9571,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P76" s="22" t="inlineStr">
+      <c r="P76" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q76" s="22" t="inlineStr">
+      <c r="R76" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R76" s="21" t="inlineStr">
+      <c r="S76" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S76" s="18" t="inlineStr">
+      <c r="T76" s="18" t="inlineStr">
         <is>
           <t>The largest single block of clinician time this initiative can hand back. The one-pager now commits to automating the round and to keeping the schedule pliable until confirmation, so changes can land before the patient is told. The care in the design is that the call also surfaces things a reminder never would.</t>
         </is>
       </c>
-      <c r="T76" s="18" t="inlineStr">
+      <c r="U76" s="18" t="inlineStr">
         <is>
           <t>How do we automate the round without losing what the conversation catches?</t>
         </is>
@@ -9245,27 +9674,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P77" s="22" t="inlineStr">
+      <c r="P77" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q77" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q77" s="22" t="inlineStr">
+      <c r="R77" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R77" s="21" t="inlineStr">
+      <c r="S77" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S77" s="18" t="inlineStr">
+      <c r="T77" s="18" t="inlineStr">
         <is>
           <t>Deterministic and safe. This is the most obvious quick win in the engagement arena.</t>
         </is>
       </c>
-      <c r="T77" s="18" t="inlineStr">
+      <c r="U77" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -9343,27 +9777,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P78" s="22" t="inlineStr">
+      <c r="P78" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q78" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q78" s="22" t="inlineStr">
+      <c r="R78" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R78" s="21" t="inlineStr">
+      <c r="S78" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S78" s="18" t="inlineStr">
+      <c r="T78" s="18" t="inlineStr">
         <is>
           <t>Deterministic from position and route. Note it implies clinician location tracking, which is a conversation to have deliberately.</t>
         </is>
       </c>
-      <c r="T78" s="18" t="inlineStr">
+      <c r="U78" s="18" t="inlineStr">
         <is>
           <t>Are we comfortable with the location tracking this implies, and have clinicians been consulted?</t>
         </is>
@@ -9441,27 +9880,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P79" s="22" t="inlineStr">
+      <c r="P79" s="20" t="inlineStr">
+        <is>
+          <t>At start of care</t>
+        </is>
+      </c>
+      <c r="Q79" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q79" s="22" t="inlineStr">
+      <c r="R79" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R79" s="21" t="inlineStr">
+      <c r="S79" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S79" s="18" t="inlineStr">
+      <c r="T79" s="18" t="inlineStr">
         <is>
           <t>Honour it, never assume it. Conflict risk: a vendor with its own communication model may not respect an existing preference store. Consent and opt-out rules also carry regulatory weight.</t>
         </is>
       </c>
-      <c r="T79" s="18" t="inlineStr">
+      <c r="U79" s="18" t="inlineStr">
         <is>
           <t>Where would channel preference and consent live, and who captures it at admission?</t>
         </is>
@@ -9543,27 +9987,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P80" s="22" t="inlineStr">
+      <c r="P80" s="20" t="inlineStr">
+        <is>
+          <t>At referral / welcome call</t>
+        </is>
+      </c>
+      <c r="Q80" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q80" s="22" t="inlineStr">
+      <c r="R80" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R80" s="21" t="inlineStr">
+      <c r="S80" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S80" s="18" t="inlineStr">
+      <c r="T80" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug. The failure it prevents is concrete: a nurse arrives for the start of care, the patient cannot sign, and the power of attorney is two states away. The visit is wasted and the clock keeps running.</t>
         </is>
       </c>
-      <c r="T80" s="18" t="inlineStr">
+      <c r="U80" s="18" t="inlineStr">
         <is>
           <t>Where would POA status be captured so the scheduler sees it before booking rather than after?</t>
         </is>
@@ -9641,27 +10090,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P81" s="22" t="inlineStr">
+      <c r="P81" s="20" t="inlineStr">
+        <is>
+          <t>At referral / welcome call</t>
+        </is>
+      </c>
+      <c r="Q81" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q81" s="22" t="inlineStr">
+      <c r="R81" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R81" s="21" t="inlineStr">
+      <c r="S81" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S81" s="18" t="inlineStr">
+      <c r="T81" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and distinct from channel preference: a preference is no use without a working number for the right party. The failure it names is reminders going to a disconnected mobile while the daughter who books every visit is never contacted.</t>
         </is>
       </c>
-      <c r="T81" s="18" t="inlineStr">
+      <c r="U81" s="18" t="inlineStr">
         <is>
           <t>Who verifies the number, and at what point in admission?</t>
         </is>
@@ -9739,27 +10193,32 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="P82" s="22" t="inlineStr">
+      <c r="P82" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q82" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q82" s="22" t="inlineStr">
+      <c r="R82" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R82" s="21" t="inlineStr">
+      <c r="S82" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S82" s="18" t="inlineStr">
+      <c r="T82" s="18" t="inlineStr">
         <is>
           <t>Added 19 Aug, and it puts a hard boundary on the automation the one-pager promises: consents are signed at the start-of-care visit, so no automated texting can precede admission and the readiness call before that first visit is necessarily a voice call.</t>
         </is>
       </c>
-      <c r="T82" s="18" t="inlineStr">
+      <c r="U82" s="18" t="inlineStr">
         <is>
           <t>Does this change what we can promise vendors about pre-admission outreach?</t>
         </is>
@@ -9841,27 +10300,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P83" s="22" t="inlineStr">
+      <c r="P83" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q83" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q83" s="22" t="inlineStr">
+      <c r="R83" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R83" s="21" t="inlineStr">
+      <c r="S83" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S83" s="18" t="inlineStr">
+      <c r="T83" s="18" t="inlineStr">
         <is>
           <t>Human negotiation around a moving constraint. Note that when rapid reschedule is switched on, a clinician moving their own visit inside the week creates no office work at all — so the volume the office sees is a branch configuration choice, not a fact.</t>
         </is>
       </c>
-      <c r="T83" s="18" t="inlineStr">
+      <c r="U83" s="18" t="inlineStr">
         <is>
           <t>Which branches have rapid reschedule enabled? It changes what the office actually sees.</t>
         </is>
@@ -9943,27 +10407,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P84" s="22" t="inlineStr">
+      <c r="P84" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q84" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q84" s="22" t="inlineStr">
+      <c r="R84" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R84" s="21" t="inlineStr">
+      <c r="S84" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S84" s="18" t="inlineStr">
+      <c r="T84" s="18" t="inlineStr">
         <is>
           <t>Detection is clean; the recovery pulls in every soft constraint again.</t>
         </is>
       </c>
-      <c r="T84" s="18" t="inlineStr">
+      <c r="U84" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -10045,27 +10514,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P85" s="22" t="inlineStr">
+      <c r="P85" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q85" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q85" s="22" t="inlineStr">
+      <c r="R85" s="22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R85" s="21" t="inlineStr">
+      <c r="S85" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S85" s="18" t="inlineStr">
+      <c r="T85" s="18" t="inlineStr">
         <is>
           <t>Runs on the same relational willingness as the per-diem and elasticity rows. A system can assemble the candidate list and reach people directly; it cannot decide who will say yes. This is where an incentive on a hard-to-fill visit would attach.</t>
         </is>
       </c>
-      <c r="T85" s="18" t="inlineStr">
+      <c r="U85" s="18" t="inlineStr">
         <is>
           <t>Would we let the system contact clinicians directly with an open visit, or must a person always make the ask?</t>
         </is>
@@ -10147,27 +10621,32 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
-      <c r="P86" s="22" t="inlineStr">
+      <c r="P86" s="20" t="inlineStr">
+        <is>
+          <t>On event — coverage and surge</t>
+        </is>
+      </c>
+      <c r="Q86" s="22" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Q86" s="22" t="inlineStr">
+      <c r="R86" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R86" s="21" t="inlineStr">
+      <c r="S86" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S86" s="18" t="inlineStr">
+      <c r="T86" s="18" t="inlineStr">
         <is>
           <t>A genuine gap, not an oversight: this was added to the vendor ask on 21 Aug and the 19 Aug inventory predates it. Recorded here so the workbook and the questionnaire stay aligned. Next free IDs after 19 Aug are SH-10, C-15, S-51 and CO-15.</t>
         </is>
       </c>
-      <c r="T86" s="18" t="inlineStr">
+      <c r="U86" s="18" t="inlineStr">
         <is>
           <t>Do we add this to the variable inventory as a new ID? It is currently asked of vendors but not modelled by us.</t>
         </is>
@@ -10249,27 +10728,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P87" s="22" t="inlineStr">
+      <c r="P87" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q87" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q87" s="22" t="inlineStr">
+      <c r="R87" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R87" s="21" t="inlineStr">
+      <c r="S87" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S87" s="18" t="inlineStr">
+      <c r="T87" s="18" t="inlineStr">
         <is>
           <t>Rule-informed but bounded by what a patient will tolerate in a week. Propose, do not dictate.</t>
         </is>
       </c>
-      <c r="T87" s="18" t="inlineStr">
+      <c r="U87" s="18" t="inlineStr">
         <is>
           <t>Is there a standard on how many visits a patient should have in one day?</t>
         </is>
@@ -10351,27 +10835,32 @@
           <t>This is the contact</t>
         </is>
       </c>
-      <c r="P88" s="22" t="inlineStr">
+      <c r="P88" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q88" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q88" s="22" t="inlineStr">
+      <c r="R88" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R88" s="21" t="inlineStr">
+      <c r="S88" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S88" s="18" t="inlineStr">
+      <c r="T88" s="18" t="inlineStr">
         <is>
           <t>Logging and notifying is automatable; deciding what deserves an escalation is human judgment.</t>
         </is>
       </c>
-      <c r="T88" s="18" t="inlineStr">
+      <c r="U88" s="18" t="inlineStr">
         <is>
           <t>Nothing outstanding.</t>
         </is>
@@ -10453,34 +10942,39 @@
           <t>Live / computed</t>
         </is>
       </c>
-      <c r="P89" s="22" t="inlineStr">
+      <c r="P89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q89" s="22" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="Q89" s="22" t="inlineStr">
+      <c r="R89" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R89" s="21" t="inlineStr">
+      <c r="S89" s="21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S89" s="18" t="inlineStr">
+      <c r="T89" s="18" t="inlineStr">
         <is>
           <t>Measure and surface it; do not try to control the people doing it. This is the number that turns the business case from theory into a figure the branch recognises.</t>
         </is>
       </c>
-      <c r="T89" s="18" t="inlineStr">
+      <c r="U89" s="18" t="inlineStr">
         <is>
           <t>Is there an appetite to measure this directly, or should it be estimated from the automation we remove?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T89"/>
+  <autoFilter ref="A1:U89"/>
   <conditionalFormatting sqref="J2:K89">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$K2="High"</formula>
@@ -10492,18 +10986,18 @@
       <formula>$K2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R89">
+  <conditionalFormatting sqref="S2:S89">
     <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
-      <formula>$R2="High"</formula>
+      <formula>$S2="High"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="0">
-      <formula>$R2="Medium"</formula>
+      <formula>$S2="Medium"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="0">
-      <formula>$R2="Low"</formula>
+      <formula>$S2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="B2:B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$A$2:$A$4</formula1>
     </dataValidation>
@@ -10513,13 +11007,13 @@
     <dataValidation sqref="L2:L89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -10527,6 +11021,9 @@
     </dataValidation>
     <dataValidation sqref="O2:O89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$I$2:$I$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$J$2:$J$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10539,7 +11036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10551,6 +11048,7 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10599,6 +11097,11 @@
           <t>Stays true on its own?</t>
         </is>
       </c>
+      <c r="J1" s="26" t="inlineStr">
+        <is>
+          <t>Re-checked when</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
@@ -10646,6 +11149,11 @@
           <t>Stable</t>
         </is>
       </c>
+      <c r="J2" s="27" t="inlineStr">
+        <is>
+          <t>At referral / welcome call</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
@@ -10693,6 +11201,11 @@
           <t>Drifts — needs re-contact</t>
         </is>
       </c>
+      <c r="J3" s="27" t="inlineStr">
+        <is>
+          <t>At start of care</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
@@ -10735,6 +11248,11 @@
           <t>Live / computed</t>
         </is>
       </c>
+      <c r="J4" s="27" t="inlineStr">
+        <is>
+          <t>Weekly — when the week is built</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="C5" s="27" t="inlineStr">
@@ -10762,6 +11280,11 @@
           <t>This is the contact</t>
         </is>
       </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>Day before — the confirmation round</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="G6" s="27" t="inlineStr">
@@ -10774,6 +11297,11 @@
           <t>Clinician</t>
         </is>
       </c>
+      <c r="J6" s="27" t="inlineStr">
+        <is>
+          <t>At recertification</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="G7" s="27" t="inlineStr">
@@ -10786,6 +11314,11 @@
           <t>Clinical Manager</t>
         </is>
       </c>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>On event — coverage and surge</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="G8" s="27" t="inlineStr">
@@ -10798,6 +11331,11 @@
           <t>Branch Leadership (ED)</t>
         </is>
       </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>Not re-checked today</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="G9" s="27" t="inlineStr">
@@ -10808,6 +11346,11 @@
       <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Per Diem / Float</t>
+        </is>
+      </c>
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
@@ -1033,7 +1033,7 @@
     <row r="33">
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D33" s="12">
-        <f>COUNTIF('Master List'!$B$2:$B$89,"Patient Engagement")</f>
+        <f>COUNTIF('Master List'!$B$2:$B$89,"Engagement")</f>
         <v/>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D44" s="12">
-        <f>COUNTIFS('Master List'!$O$2:$O$89,"Drifts*",'Master List'!$B$2:$B$89,"&lt;&gt;Patient Engagement")</f>
+        <f>COUNTIFS('Master List'!$O$2:$O$89,"Drifts*",'Master List'!$B$2:$B$89,"&lt;&gt;Engagement")</f>
         <v/>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr"/>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr"/>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C79" s="18" t="inlineStr"/>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr"/>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr"/>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C83" s="18" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C87" s="18" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C89" s="18" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Patient Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
@@ -11210,7 +11210,7 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>Patient Engagement</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="B4" s="27" t="inlineStr">

--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
@@ -786,127 +786,127 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Straight from the Module column of the 19 Aug workbook. That column is authoritative — change it there, not here.</t>
+          <t>One of the three project categories: Capacity Management, Scheduling, Engagement. Placement is straight from the Module column of the 19 Aug workbook, which is authoritative — change it there, not here. Only the names are shortened to match the one-pager (the workbook writes the third one as “Patient Engagement”).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Also touches</t>
+          <t>What Engagement covers</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>The other arenas the variable shows up in. Plenty are shared — that is expected, not a problem to resolve.</t>
+          <t>Not only the patient. Engagement is the contact work that turns a schedule into delivered visits, whoever it is with — office to clinician, clinician back to the office, clinician to clinician, and the care team to each other, as well as the patient and their caregiver. Finding coverage for a call-out is engagement; so is keeping the case manager in step. The one-pager already says so: “with patients, clinicians and the office.”</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>One-pager group</t>
+          <t>Also touches</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>The ten group headings from the vendor one-pager. Part B of the questionnaire scores exactly these groups.</t>
+          <t>The other arenas the variable shows up in. Plenty are shared — that is expected, not a problem to resolve.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Placement check</t>
+          <t>One-pager group</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Whether the workbook and the one-pager agree on where this belongs. They disagree on a number of rows — neither is wrong, the workbook is the internal model and the one-pager is the vendor view, but a vendor answering under one heading while we score under another gives a false coverage read. The disagreements are surfaced here rather than resolved.</t>
+          <t>The ten group headings from the vendor one-pager. Part B of the questionnaire scores exactly these groups.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>In plain terms</t>
+          <t>Placement check</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Written for a reader with no home-health background. If a sentence needs clinical knowledge to parse, it needs rewriting.</t>
+          <t>Whether the workbook and the one-pager agree on where this belongs. They disagree on a number of rows — neither is wrong, the workbook is the internal model and the one-pager is the vendor view, but a vendor answering under one heading while we score under another gives a false coverage read. The disagreements are surfaced here rather than resolved.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Who does the work today</t>
+          <t>In plain terms</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>The role that physically performs the task. Shared ownership is fine — 'DCS and Scheduler' is a real answer.</t>
+          <t>Written for a reader with no home-health background. If a sentence needs clinical knowledge to parse, it needs rewriting.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Who reads it and decides today</t>
+          <t>Who does the work today</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>The role that looks at the result and acts. Often a different person from the one who does the work, and sometimes the honest answer is nobody — those rows are marked '— no one today' and they are the interesting ones.</t>
+          <t>The role that physically performs the task. Shared ownership is fine — 'DCS and Scheduler' is a real answer.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Where the information lives today</t>
+          <t>Who reads it and decides today</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>The system, screen or note it sits in. Shaded by how sure we are — see the confidence key below.</t>
+          <t>The role that looks at the result and acts. Often a different person from the one who does the work, and sometimes the honest answer is nobody — those rows are marked '— no one today' and they are the interesting ones.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Future state -- the tool's role</t>
+          <t>Where the information lives today</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Automate (the tool does it), Assist (the tool proposes, a person confirms), Surface (the tool shows, a person decides), Stays manual (unchanged).</t>
+          <t>The system, screen or note it sits in. Shaded by how sure we are — see the confidence key below.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Future state -- who decides</t>
+          <t>Future state -- the tool's role</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>For Assist and Surface rows, the person who confirms or acts. For Automate rows, who owns the exception when automation cannot resolve it.</t>
+          <t>Automate (the tool does it), Assist (the tool proposes, a person confirms), Surface (the tool shows, a person decides), Stays manual (unchanged).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Trigger / how often</t>
+          <t>Future state -- who decides</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>What sets the task off and at what rhythm. This is the column the future-state maps are built from — a map is a sequence of triggers.</t>
+          <t>For Assist and Surface rows, the person who confirms or acts. For Automate rows, who owns the exception when automation cannot resolve it.</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Stable = record it once and it holds. Drifts = it goes stale unless somebody keeps asking, so it needs a standing engagement mechanism, not a field captured at start of care. Live/computed = recalculated, no decay problem. This is the contact = the row is the outbound work itself.</t>
+          <t>What sets the task off and at what rhythm. This is the column the future-state maps are built from — a map is a sequence of triggers.</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>COUNTIF('Master List'!$B$2:$B$89,"Scheduling Engine")</f>
+        <f>COUNTIF('Master List'!$B$2:$B$89,"Scheduling")</f>
         <v/>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr"/>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr"/>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr"/>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr"/>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr"/>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F69" s="18" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling Engine</t>
+          <t>Differs — the one-pager groups this under Scheduling</t>
         </is>
       </c>
       <c r="F73" s="18" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>Scheduling Engine</t>
+          <t>Scheduling</t>
         </is>
       </c>
       <c r="B3" s="27" t="inlineStr">

--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Variable-Workbook.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>One of the three project categories: Capacity Management, Scheduling, Engagement. Placement is straight from the Module column of the 19 Aug workbook, which is authoritative — change it there, not here. Only the names are shortened to match the one-pager (the workbook writes the third one as “Patient Engagement”).</t>
+          <t>One of the three project categories: Capacity Management, Scheduling Engine, Engagement. Placement is straight from the Module column of the 19 Aug workbook, which is authoritative — change it there, not here. The only renaming is “Patient Engagement” → “Engagement”, to match the one-pager.</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Not only the patient. Engagement is the contact work that turns a schedule into delivered visits, whoever it is with — office to clinician, clinician back to the office, clinician to clinician, and the care team to each other, as well as the patient and their caregiver. Finding coverage for a call-out is engagement; so is keeping the case manager in step. The one-pager already says so: “with patients, clinicians and the office.”</t>
+          <t>Not only the patient — which is exactly why the label was shortened. Engagement is the contact work that turns a schedule into delivered visits, whoever it is with: office to clinician, clinician back to the office, clinician to clinician, and the care team to each other, as well as the patient and their caregiver. Finding coverage for a call-out is engagement; so is keeping the case manager in step. The one-pager already says so: “with patients, clinicians and the office.”</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>COUNTIF('Master List'!$B$2:$B$89,"Scheduling")</f>
+        <f>COUNTIF('Master List'!$B$2:$B$89,"Scheduling Engine")</f>
         <v/>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr"/>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr"/>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr"/>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr"/>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr"/>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F69" s="18" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Differs — the one-pager groups this under Scheduling</t>
+          <t>Differs — the one-pager groups this under Scheduling Engine</t>
         </is>
       </c>
       <c r="F73" s="18" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling; write this back to the workbook</t>
+          <t>Ruled 25 Aug — moved to Engagement. The 8.19 workbook still has it under Scheduling Engine; write this back to the workbook</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>Scheduling Engine</t>
         </is>
       </c>
       <c r="B3" s="27" t="inlineStr">
